--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -11676,7 +11676,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr">
+      <c r="I246" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/j6NAC1lVkB4</t>
         </is>
@@ -11716,7 +11716,12 @@
       </c>
       <c r="H247" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I247" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/OKtwYjKgk6M</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11759,12 @@
       </c>
       <c r="H248" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I248" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/hFBOz0gge3Q</t>
         </is>
       </c>
     </row>
@@ -11792,7 +11802,12 @@
       </c>
       <c r="H249" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>https://youtu.be/vy2na1KvSgc</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -11805,7 +11805,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr">
+      <c r="I249" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/vy2na1KvSgc</t>
         </is>
@@ -11845,7 +11845,12 @@
       </c>
       <c r="H250" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I250" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/EK33vmYd_7Y</t>
         </is>
       </c>
     </row>
@@ -11883,7 +11888,12 @@
       </c>
       <c r="H251" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I251" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Z6I3f4YBWlQ</t>
         </is>
       </c>
     </row>
@@ -11921,7 +11931,12 @@
       </c>
       <c r="H252" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>https://youtu.be/kopLfrc6VnA</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -11934,7 +11934,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr">
+      <c r="I252" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/kopLfrc6VnA</t>
         </is>
@@ -11974,7 +11974,12 @@
       </c>
       <c r="H253" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I253" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/wV7SBxEzdtE</t>
         </is>
       </c>
     </row>
@@ -12012,7 +12017,12 @@
       </c>
       <c r="H254" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I254" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/RToLeNozqf4</t>
         </is>
       </c>
     </row>
@@ -12050,7 +12060,12 @@
       </c>
       <c r="H255" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>https://youtu.be/V-__dObXxk4</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -12063,7 +12063,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr">
+      <c r="I255" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/V-__dObXxk4</t>
         </is>
@@ -12103,7 +12103,12 @@
       </c>
       <c r="H256" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I256" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ZJaHzhEJuxc</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12146,12 @@
       </c>
       <c r="H257" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I257" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/w9hvwHKXORI</t>
         </is>
       </c>
     </row>
@@ -12179,7 +12189,12 @@
       </c>
       <c r="H258" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>https://youtu.be/A165mjfc_0M</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -12192,7 +12192,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr">
+      <c r="I258" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/A165mjfc_0M</t>
         </is>
@@ -12232,7 +12232,12 @@
       </c>
       <c r="H259" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I259" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/uTte9AL3xsU</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12275,12 @@
       </c>
       <c r="H260" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I260" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/uiKv3jEeFyk</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12318,12 @@
       </c>
       <c r="H261" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>https://youtu.be/GiooV0EAzhY</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -12321,7 +12321,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr">
+      <c r="I261" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/GiooV0EAzhY</t>
         </is>
@@ -12361,7 +12361,12 @@
       </c>
       <c r="H262" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I262" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/fVoFD57ZqD4</t>
         </is>
       </c>
     </row>
@@ -12399,7 +12404,12 @@
       </c>
       <c r="H263" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I263" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/BwJp8n_jLDc</t>
         </is>
       </c>
     </row>
@@ -12437,7 +12447,12 @@
       </c>
       <c r="H264" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>https://youtu.be/HfRt7LgdQLo</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -12450,7 +12450,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr">
+      <c r="I264" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/HfRt7LgdQLo</t>
         </is>
@@ -12490,7 +12490,12 @@
       </c>
       <c r="H265" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I265" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/R8B1934R_54</t>
         </is>
       </c>
     </row>
@@ -12528,7 +12533,12 @@
       </c>
       <c r="H266" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I266" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/tNBt0fGTPiY</t>
         </is>
       </c>
     </row>
@@ -12566,7 +12576,12 @@
       </c>
       <c r="H267" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>https://youtu.be/l-15DyPDicY</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -12579,7 +12579,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr">
+      <c r="I267" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/l-15DyPDicY</t>
         </is>
@@ -12619,7 +12619,12 @@
       </c>
       <c r="H268" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I268" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/XIDMopsGg60</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12662,12 @@
       </c>
       <c r="H269" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I269" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/T3wU9mEOhJA</t>
         </is>
       </c>
     </row>
@@ -12695,7 +12705,12 @@
       </c>
       <c r="H270" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>https://youtu.be/AhL8uN_aKDA</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -12708,7 +12708,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr">
+      <c r="I270" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/AhL8uN_aKDA</t>
         </is>
@@ -12748,7 +12748,12 @@
       </c>
       <c r="H271" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I271" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/16C4MPHAtks</t>
         </is>
       </c>
     </row>
@@ -12786,7 +12791,12 @@
       </c>
       <c r="H272" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I272" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/gtmMRfKyMuU</t>
         </is>
       </c>
     </row>
@@ -12824,7 +12834,12 @@
       </c>
       <c r="H273" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>https://youtu.be/X4oIjlQjEcw</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -12837,7 +12837,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr">
+      <c r="I273" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/X4oIjlQjEcw</t>
         </is>
@@ -12877,7 +12877,12 @@
       </c>
       <c r="H274" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I274" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ayKro1d4nGk</t>
         </is>
       </c>
     </row>
@@ -12915,7 +12920,12 @@
       </c>
       <c r="H275" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I275" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/NImxIkRX4j4</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12963,12 @@
       </c>
       <c r="H276" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>https://youtu.be/LQFtYRXEqA8</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -12966,7 +12966,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr">
+      <c r="I276" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/LQFtYRXEqA8</t>
         </is>
@@ -13006,7 +13006,12 @@
       </c>
       <c r="H277" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I277" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/7rvMgXH8Ggk</t>
         </is>
       </c>
     </row>
@@ -13044,7 +13049,12 @@
       </c>
       <c r="H278" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I278" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/6ro6GqL8V74</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13092,12 @@
       </c>
       <c r="H279" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>https://youtu.be/N4cUX8blnM4</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -13095,7 +13095,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr">
+      <c r="I279" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/N4cUX8blnM4</t>
         </is>
@@ -13135,7 +13135,12 @@
       </c>
       <c r="H280" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I280" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/cdxCucBU7wM</t>
         </is>
       </c>
     </row>
@@ -13173,7 +13178,12 @@
       </c>
       <c r="H281" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I281" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/z_YZq0uzlLU</t>
         </is>
       </c>
     </row>
@@ -13211,7 +13221,12 @@
       </c>
       <c r="H282" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>https://youtu.be/rPKzJ-zPF4E</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -13224,7 +13224,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr">
+      <c r="I282" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/rPKzJ-zPF4E</t>
         </is>
@@ -13264,7 +13264,12 @@
       </c>
       <c r="H283" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I283" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/6-MLMolipPg</t>
         </is>
       </c>
     </row>
@@ -13302,7 +13307,12 @@
       </c>
       <c r="H284" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I284" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/30XvHcuBrTA</t>
         </is>
       </c>
     </row>
@@ -13340,7 +13350,12 @@
       </c>
       <c r="H285" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>https://youtu.be/am3MTNlvZ_Y</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -13353,7 +13353,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr">
+      <c r="I285" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/am3MTNlvZ_Y</t>
         </is>
@@ -13393,7 +13393,12 @@
       </c>
       <c r="H286" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I286" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/7cV4rFyBXvQ</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13436,12 @@
       </c>
       <c r="H287" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I287" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/yIQFGpvGMj0</t>
         </is>
       </c>
     </row>
@@ -13469,7 +13479,12 @@
       </c>
       <c r="H288" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>https://youtu.be/p9TCPqvSR1Q</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -13482,7 +13482,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr">
+      <c r="I288" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/p9TCPqvSR1Q</t>
         </is>
@@ -13522,7 +13522,12 @@
       </c>
       <c r="H289" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I289" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/UweY3r2FdiI</t>
         </is>
       </c>
     </row>
@@ -13560,7 +13565,12 @@
       </c>
       <c r="H290" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I290" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/RGP4bpiidPE</t>
         </is>
       </c>
     </row>
@@ -13598,7 +13608,12 @@
       </c>
       <c r="H291" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>https://youtu.be/z6Tnb45OITY</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -13611,7 +13611,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr">
+      <c r="I291" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/z6Tnb45OITY</t>
         </is>
@@ -13651,7 +13651,12 @@
       </c>
       <c r="H292" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I292" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/GeVzy56rT-o</t>
         </is>
       </c>
     </row>
@@ -13689,7 +13694,12 @@
       </c>
       <c r="H293" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I293" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/Q5Cl2f83LI8</t>
         </is>
       </c>
     </row>
@@ -13727,7 +13737,12 @@
       </c>
       <c r="H294" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>https://youtu.be/kabbdDLfodg</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -13740,7 +13740,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr">
+      <c r="I294" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/kabbdDLfodg</t>
         </is>
@@ -13780,7 +13780,12 @@
       </c>
       <c r="H295" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I295" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/sghLPEo7qAQ</t>
         </is>
       </c>
     </row>
@@ -13818,7 +13823,12 @@
       </c>
       <c r="H296" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I296" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/uKAYV_adCas</t>
         </is>
       </c>
     </row>
@@ -13856,7 +13866,12 @@
       </c>
       <c r="H297" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>https://youtu.be/wbBz0FplNT8</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -13869,7 +13869,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr">
+      <c r="I297" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/wbBz0FplNT8</t>
         </is>
@@ -13909,7 +13909,12 @@
       </c>
       <c r="H298" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I298" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/8ZrBznvfBJI</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13952,12 @@
       </c>
       <c r="H299" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I299" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/VmjXsJ8MyMw</t>
         </is>
       </c>
     </row>
@@ -13985,7 +13995,12 @@
       </c>
       <c r="H300" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>https://youtu.be/T7vgumUqihw</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -13998,7 +13998,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr">
+      <c r="I300" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/T7vgumUqihw</t>
         </is>
@@ -14038,7 +14038,12 @@
       </c>
       <c r="H301" s="31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>https://youtu.be/x43rf43ibmo</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I301"/>
+  <dimension ref="A1:I451"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="31" min="1" max="1"/>
@@ -14041,9 +14041,5709 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="I301" t="inlineStr">
+      <c r="I301" s="31" t="inlineStr">
         <is>
           <t>https://youtu.be/x43rf43ibmo</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="n">
+        <v>43</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>I grip and I pinch with two jaws of steel, bending the wire that won't easily yield. What am I?</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Pliers</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="n">
+        <v>44</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Struck on my head, I bite into wood or stone, shaving off slivers to leave shapes alone. What am I?</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>A chisel</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="n">
+        <v>44</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Rough on one side, I rub away the old, smoothing the splinters till the surface is bold. What am I?</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Sandpaper</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="n">
+        <v>44</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>A bubble lives in me and floats to the top; I tell you when to build and when to stop. What am I?</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>A spirit level</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="n">
+        <v>44</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>I roll out in inches then snap back inside; how long is it? I'm the one you confide. What am I?</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>A tape measure</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="n">
+        <v>44</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>I hold two pieces in a stubborn embrace while the glue dries slowly into place. What am I?</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>A clamp</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="n">
+        <v>44</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Heavy and horned, I take every blow; the blacksmith shapes metal on me, you know. What am I?</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>An anvil</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="n">
+        <v>44</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Step on my shoulder and I bite the ground, lifting the earth in a heap all around. What am I?</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>A shovel</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="n">
+        <v>45</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>With fingers of metal but no hand at all, I gather the leaves when they start to fall. What am I?</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>A rake</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="n">
+        <v>45</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>One wheel in front and two legs behind, I carry your load of the heavy kind. What am I?</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>A wheelbarrow</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="n">
+        <v>45</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>A wedge on a handle, I swing and I split; the logs fall in two where my sharp edge is hit. What am I?</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>An axe</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="n">
+        <v>45</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>I melt a silver thread to bond two wires tight, hot at my tip with a wisp of white. What am I?</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>A soldering iron</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="n">
+        <v>45</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Bolted to the bench, I squeeze and I clench, holding your work in an iron pinch. What am I?</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>A vise</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="n">
+        <v>45</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>A little flat blade for the gardener's hand, I dig the small holes where the seedlings stand. What am I?</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>A trowel</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="n">
+        <v>45</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Long tines on a pole, I toss the hay high; the farmer lifts bundles as the barn stays dry. What am I?</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>A pitchfork</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" t="n">
+        <v>46</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Full of small holes, I let the fine through while keeping the lumps that won't pass for you. What am I?</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>A sieve</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" t="n">
+        <v>46</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>I shave off the skin in a ribbon so thin, before the potato goes into the tin. What am I?</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>A peeler</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" t="n">
+        <v>46</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Two arms and a hinge, I pinch and I grab the hot and the slippery off of the slab. What am I?</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Tongs</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" t="n">
+        <v>46</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Lines on my side say how much to pour; stop at the mark and you'll need no more. What am I?</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>A measuring cup</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" t="n">
+        <v>46</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>I steep the leaves and I hold the brew, a lid on my top and a spout to pour through. What am I?</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>A teapot</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" t="n">
+        <v>46</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Hot stays hot and cold stays cold inside my double-walled hold. What am I?</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>A thermos</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" t="n">
+        <v>46</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>I sit on your lap through the whole of the meal, catching the drips that your fingers conceal. What am I?</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>A napkin</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" t="n">
+        <v>47</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>I plug up the bottle to keep the wine sealed, then pop with a bang when the glass is revealed. What am I?</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>A cork</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" t="n">
+        <v>47</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Glass with a lid that you twist to undo, I keep the jam fresh the whole winter through. What am I?</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>A jar</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" t="n">
+        <v>47</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>I slide out and in on a runner or two, holding your socks and your odds and ends too. What am I?</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>A drawer</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" t="n">
+        <v>47</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Flat on the wall, I hold up your books; I ask for no thanks for the way the room looks. What am I?</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>A shelf</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" t="n">
+        <v>47</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Slung between trees, I sway you to sleep; no legs of my own, just a gentle sweep. What am I?</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>A hammock</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" t="n">
+        <v>47</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>I move back and forth but go nowhere at all, soothing the baby or the grandmother tall. What am I?</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>A rocking chair</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" t="n">
+        <v>47</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>I hang from the ceiling with crystals that gleam, dripping with light like a frozen stream. What am I?</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>A chandelier</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" t="n">
+        <v>48</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Ribbed and warm by the wall I stand, hissing out heat when the winter's at hand. What am I?</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>A radiator</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" t="n">
+        <v>48</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>I open at dawn and I close for the night, keeping the bedroom away from the light. What am I?</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>A curtain</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" t="n">
+        <v>48</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Soft underfoot and spread on the floor, I warm your toes from wall to door. What am I?</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>A carpet</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" t="n">
+        <v>48</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>I soften the glare of the bulb I surround, a hat for the light that it casts around. What am I?</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>A lampshade</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" t="n">
+        <v>48</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Three legs or four and no back to lean, I'm the shortest seat that you've ever seen. What am I?</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>A stool</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" t="n">
+        <v>48</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>A brim at the front to shade your eyes, I sit on your head beneath sunny skies. What am I?</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>A cap</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" t="n">
+        <v>48</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>A band over the top and a muff on each ear, I keep out the cold when winter is near. What am I?</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Earmuffs</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" t="n">
+        <v>49</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Criss-crossed and knotted, I hold the shoe tight; undo me too loose and you'll trip in the night. What am I?</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>A shoelace</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" t="n">
+        <v>49</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>I sit at the collar in a neat little knot, dressing you up for the fancy spot. What am I?</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>A bowtie</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" t="n">
+        <v>49</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Metal and prong, I fasten the strap, cinching the belt with a satisfying snap. What am I?</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>A buckle</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" t="n">
+        <v>49</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>A circle of beads round the wrist I lie, jingling softly as the hand goes by. What am I?</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>A bracelet</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" t="n">
+        <v>49</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Thin and sheer, I cover the face, lifted at last in a moment of grace. What am I?</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>A veil</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" t="n">
+        <v>49</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Six-sided rooms in a wall of gold, I store the sweet that the bees have told. What am I?</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>A honeycomb</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" t="n">
+        <v>49</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Spun in the corner on threads so fine, I catch the fly in a silken line. What am I?</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>A spider's web</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" t="n">
+        <v>50</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>I wrap up a crawler in silk nice and tight; it sleeps and transforms, then takes to flight. What am I?</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>A cocoon</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" t="n">
+        <v>50</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Woven of twigs in the fork of a tree, I cradle the eggs till they're ready and free. What am I?</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>A nest</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" t="n">
+        <v>50</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Light as can be, I fall without sound; I helped a bird fly before touching the ground. What am I?</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>A feather</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" t="n">
+        <v>50</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Branched like a tree on the head of a deer, I'm shed every year and grow back next year. What am I?</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>An antler</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" t="n">
+        <v>50</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>I look like a plant but I'm built by small creatures, a reef full of color with limestone features. What am I?</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Coral</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" t="n">
+        <v>50</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>I unroll my fronds from a tight little curl, in the shade of the forest I slowly unfurl. What am I?</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>A fern</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" t="n">
+        <v>50</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>I climb up the wall with a grip and a twist, reaching for sunlight I cannot resist. What am I?</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>A vine</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" t="n">
+        <v>51</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>I blur the whole morning and swallow the hill; you drive through me slowly, the air damp and still. What am I?</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Fog</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" t="n">
+        <v>51</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>I paint the window in feathers of white, laid down by the cold in the dark of the night. What am I?</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Frost</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" t="n">
+        <v>51</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>I fall from the storm as a pellet of ice, bouncing on rooftops — not gentle, not nice. What am I?</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Hail</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" t="n">
+        <v>51</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>On the hot desert road I shimmer like water, a lie of the heat that leads you no farther. What am I?</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>A mirage</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" t="n">
+        <v>51</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>One body slides in front of another, and day turns to dusk as the light they smother. What am I?</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>An eclipse</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" t="n">
+        <v>51</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>A streak in the night as I burn up on high, you make a quick wish as I shoot through the sky. What am I?</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>A meteor</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" t="n">
+        <v>51</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>A whirlpool of billions of stars I hold, a spiral of light in the dark and cold. What am I?</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>A galaxy</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" t="n">
+        <v>52</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>I bead on the grass in the cool of the dawn, tiny and bright, then by noon I am gone. What am I?</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Dew</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" t="n">
+        <v>52</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>I spin the warm sea into towering walls, with a calm, quiet eye where the stillness falls. What am I?</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>A hurricane</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" t="n">
+        <v>52</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>A tiny curved hair on the rim of the eye, I guard against dust as it floats on by. What am I?</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>An eyelash</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" t="n">
+        <v>52</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>I bend in the finger and crack when you press, a hinge in the hand, more or less. What am I?</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>A knuckle</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" t="n">
+        <v>52</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>A small happy dent in the cheek I appear, only when smiling or grinning ear to ear. What am I?</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>A dimple</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" t="n">
+        <v>52</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>A speck of brown the sun brings out, scattered on noses and cheeks about. What am I?</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>A freckle</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" t="n">
+        <v>52</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>A tight little skin deep inside the ear, I quiver with sound so that you can hear. What am I?</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>An eardrum</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" t="n">
+        <v>53</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>I spread without legs and I grow as I go, started by one, soon everyone's in the know. What am I?</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>A rumor</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" t="n">
+        <v>53</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Blow out the candles or watch a star fall, say me in silence — don't tell them at all. What am I?</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>A wish</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" t="n">
+        <v>53</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>I'm what you run out of while stuck in a queue, the virtue of waiting till something comes through. What am I?</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Patience</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" t="n">
+        <v>53</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Held in the heart long after the slight, I'm heavy to carry both day and night. What am I?</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>A grudge</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" t="n">
+        <v>53</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>The hands point straight up when the old day is dead, and a brand-new one starts while you're still in bed. What am I?</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Midnight</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" t="n">
+        <v>53</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Ten trips of the earth all the way round the sun, I'm counted in tens when they're finally done. What am I?</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>A decade</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" t="n">
+        <v>53</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Once every four I add one more day, giving February its extra stay. What am I?</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>A leap year</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" t="n">
+        <v>54</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>The in-between time, not day and not night, when the sun's gone to bed but there's still a faint light. What am I?</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Twilight</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" t="n">
+        <v>54</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>I crack open the sky at the edge of the east, the first light of morning for man and for beast. What am I?</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Dawn</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" t="n">
+        <v>54</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Two brass plates that crash with a clang, the loudest I speak with a shimmering bang. What am I?</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>A cymbal</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" t="n">
+        <v>54</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>A bag full of air and some pipes in a row, I drone and I squeal when the piper lets go. What am I?</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Bagpipes</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" t="n">
+        <v>54</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Round like a drum with some strings on my face, I twang out a tune at a bluegrass pace. What am I?</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>A banjo</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" t="n">
+        <v>54</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Taller than a fiddle, I rest on the floor, bowed between knees for a deep, rich roar. What am I?</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>A cello</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" t="n">
+        <v>54</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>A tube of black wood with keys down my side, I sing with a reed when the breath is applied. What am I?</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>A clarinet</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" t="n">
+        <v>55</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Shake me in pairs and I rattle and hiss, filled up with beads for a Latin bliss. What am I?</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Maracas</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" t="n">
+        <v>55</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Dots on five lines tell the player what's next; I'm the song written down, a musical text. What am I?</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Sheet music</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" t="n">
+        <v>55</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>I follow the star on the darkened stage, a circle of brightness wherever they engage. What am I?</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>A spotlight</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" t="n">
+        <v>55</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Three-legged stand where the canvas goes, I hold up the painting while the picture grows. What am I?</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>An easel</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" t="n">
+        <v>55</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Dip me in color and sweep me around, I leave strokes of beauty without any sound. What am I?</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>A paintbrush</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" t="n">
+        <v>55</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>A little flat tile with spots in two halves; I fall in a line that collapses in halves. What am I?</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>A domino</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" t="n">
+        <v>55</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Gold and gleaming, I crown the best, lifted up high above all the rest. What am I?</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>A trophy</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" t="n">
+        <v>56</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>I stand in the lane for the runner to clear; knock me down and the judges will jeer. What am I?</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>A hurdle</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" t="n">
+        <v>56</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>A circle of numbers in red and in green, aim for my center — the best you've seen. What am I?</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>A dartboard</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" t="n">
+        <v>56</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Down the string I drop then climb back to the top, with a flick of the wrist I just won't stop. What am I?</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>A yo-yo</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" t="n">
+        <v>56</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>A flying disc you fling through the air; the dog runs to catch me, then brings me back there. What am I?</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>A frisbee</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" t="n">
+        <v>56</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Up goes one end as the other comes down; take turns in the air at the edge of the town. What am I?</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>A seesaw</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" t="n">
+        <v>56</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>A small glass sphere with a swirl inside, I roll on the ground where the children bide. What am I?</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>A marble</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" t="n">
+        <v>56</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>A thousand small pieces that lock into one; finish my picture and the challenge is done. What am I?</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>A jigsaw puzzle</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" t="n">
+        <v>57</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Walls upon walls with a path in between; find your way out of my tangled green. What am I?</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>A maze</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" t="n">
+        <v>57</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>At the back of the boat I swing left and right, steering the vessel through day and night. What am I?</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>A rudder</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" t="n">
+        <v>57</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>I spin at the front and I pull the plane, blades in a blur through the sky I sustain. What am I?</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>A propeller</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" t="n">
+        <v>57</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Pointed at both ends, I glide on the lake; paddle me forward for the journey I make. What am I?</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>A canoe</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" t="n">
+        <v>57</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>No wheels at all, I slide down the snow, carrying children to the valley below. What am I?</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>A sled</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" t="n">
+        <v>57</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>I dangle from a wire up the mountainside, swaying gently on my airborne ride. What am I?</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>A cable car</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" t="n">
+        <v>57</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>A basket below and a flame burning bright, I lift off the ground on a column of light. What am I?</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>A hot-air balloon</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" t="n">
+        <v>58</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Bright orange and ready when the ship goes down, I carry the sailors so they do not drown. What am I?</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>A lifeboat</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" t="n">
+        <v>58</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>A giant garage where the aircraft sleep, I shelter the planes that the airlines keep. What am I?</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>A hangar</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" t="n">
+        <v>58</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Four spinning rotors, I hover and fly, taking your photos from up in the sky. What am I?</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>A drone</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" t="n">
+        <v>58</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>A pen with no ink for the screen of your tablet, I draw and I tap without any gadget. What am I?</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>A stylus</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" t="n">
+        <v>58</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Charged up and ready, I ride in your bag, topping your phone when its battery sags. What am I?</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>A power bank</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" t="n">
+        <v>58</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Prove you're no robot — I ask you to squint, picking the buses or the blurry print. What am I?</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>A captcha</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" t="n">
+        <v>58</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>An audio show you can play on the go, episodes streaming wherever you go. What am I?</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>A podcast</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" t="n">
+        <v>59</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>A tiny loop that plays without sound, the same little motion going round and round. What am I?</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>A GIF</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" t="n">
+        <v>59</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Slipped between pages or saved in a tab, I remember the spot that you want to grab. What am I?</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>A bookmark</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" t="n">
+        <v>59</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>I shine a thin light down the page in a sweep, turning your paper to a file you keep. What am I?</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>A scanner</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" t="n">
+        <v>59</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>I spin in your tower and remember it all, your files and your photos both big and small. What am I?</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>A hard drive</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" t="n">
+        <v>59</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>A recipe of steps that a computer obeys, deciding what you see in a hundred small ways. What am I?</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>An algorithm</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>412</v>
+      </c>
+      <c r="B413" t="n">
+        <v>59</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Strap me to your face and the real world's gone; a make-believe place is suddenly on. What am I?</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>A VR headset</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>413</v>
+      </c>
+      <c r="B414" t="n">
+        <v>59</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Layer by layer I build up a thing, from a digital plan to a physical ring. What am I?</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>A 3D printer</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>414</v>
+      </c>
+      <c r="B415" t="n">
+        <v>60</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>I sit in the corner with blinking green lights, sharing the internet through invisible flights. What am I?</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>A router</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>415</v>
+      </c>
+      <c r="B416" t="n">
+        <v>60</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Up from the sub I poke through the sea, a tube with a mirror so the captain can see. What am I?</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>A periscope</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>416</v>
+      </c>
+      <c r="B417" t="n">
+        <v>60</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>My arms turn slow in the pushing breeze, grinding the grain or pumping with ease. What am I?</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>A windmill</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" t="n">
+        <v>60</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Stuffed with straw in a field I stand, frightening crows from the farmer's land. What am I?</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>A scarecrow</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" t="n">
+        <v>60</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Bricks in a stack on the top of the house, I carry the smoke up and out, light as a mouse. What am I?</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>A chimney</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" t="n">
+        <v>60</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Deep in the ground I hold the cool water; drop down a bucket, draw up what you sought here. What am I?</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>A well</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" t="n">
+        <v>60</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>I throw up the water then catch it again, a dance in the square for the passing men. What am I?</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>A fountain</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" t="n">
+        <v>61</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>I lift up my road to let the ships pass, then lower back down over moat or morass. What am I?</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>A drawbridge</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" t="n">
+        <v>61</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Round and round in a glass little cage, I let people in and out, all the rage. What am I?</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>A revolving door</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" t="n">
+        <v>61</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Feed me your coins and press a letter and number; a snack tumbles down from my well-lit chamber. What am I?</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>A vending machine</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" t="n">
+        <v>61</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Insert your card and punch in the code; I count out the cash that you're owed. What am I?</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>An ATM</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" t="n">
+        <v>61</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Orange and striped on the road I stand, warning the cars of the works at hand. What am I?</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>A traffic cone</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" t="n">
+        <v>61</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>A ridge in the road to slow you down, I jolt the fast drivers all over town. What am I?</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>A speed bump</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" t="n">
+        <v>61</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>A heavy round lid in the middle of the street, I hide the deep tunnels beneath your feet. What am I?</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>A manhole cover</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" t="n">
+        <v>62</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Red by the curb with a cap on each side, I give the firefighters water supplied. What am I?</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>A fire hydrant</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" t="n">
+        <v>62</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Flag up or down at the end of the drive, I hold your letters until they arrive. What am I?</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>A mailbox</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" t="n">
+        <v>62</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>I spin on the lawn in the summer heat, throwing out water with a rhythmic beat. What am I?</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>A sprinkler</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" t="n">
+        <v>62</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>I hum across the grass in rows, trimming it neat wherever it grows. What am I?</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>A lawnmower</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" t="n">
+        <v>62</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>A wall made of leaves that the gardener clips, square and green at the garden's lips. What am I?</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>A hedge</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" t="n">
+        <v>62</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Walls of glass where the plants stay warm, growing inside through the winter storm. What am I?</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>A greenhouse</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" t="n">
+        <v>62</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>A little wooden box on a pole up high, a home with a hole where the sparrows fly. What am I?</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>A birdhouse</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" t="n">
+        <v>63</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Drop in your coins through the slot on my back; I'm shaped like a pig and I keep the stack. What am I?</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>A piggy bank</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" t="n">
+        <v>63</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Turn my crank and a tune starts to play, then I pop up to give you a fright and a sway. What am I?</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>A jack-in-the-box</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" t="n">
+        <v>63</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Shake me up and a blizzard appears, over a tiny town, falling for years. What am I?</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>A snow globe</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" t="n">
+        <v>63</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Wind me up and a melody spins, a ballerina turns as the tune begins. What am I?</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>A music box</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" t="n">
+        <v>63</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>I swing on a handle with a flame held within, lighting the path through the dark and the din. What am I?</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>A lantern</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" t="n">
+        <v>63</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>A beam from my end when I'm clicked on at night, I fit in your hand and I throw out the light. What am I?</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>A flashlight</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>441</v>
+      </c>
+      <c r="B442" t="n">
+        <v>63</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>The whole world spun on a tilted stand, I show every ocean and every land. What am I?</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>A globe</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>442</v>
+      </c>
+      <c r="B443" t="n">
+        <v>64</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Beads on wires that slide to and fro, I count up the sums in an ancient row. What am I?</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>An abacus</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>443</v>
+      </c>
+      <c r="B444" t="n">
+        <v>64</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>A half-moon of plastic with numbers in a bow, I measure the angles so the students know. What am I?</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>A protractor</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>444</v>
+      </c>
+      <c r="B445" t="n">
+        <v>64</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Twist the pencil in my little hole and out come the shavings as I take my toll. What am I?</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>A pencil sharpener</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>445</v>
+      </c>
+      <c r="B446" t="n">
+        <v>64</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>I bite two round holes in the edge of the sheet so it fits in the binder, tidy and neat. What am I?</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>A hole punch</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>446</v>
+      </c>
+      <c r="B447" t="n">
+        <v>64</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>I sit on your desk doing nothing but weigh, keeping the papers from blowing away. What am I?</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>A paperweight</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>447</v>
+      </c>
+      <c r="B448" t="n">
+        <v>64</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>A little metal cap for the fingertip, I guard against the needle's prick and slip. What am I?</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>A thimble</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>448</v>
+      </c>
+      <c r="B449" t="n">
+        <v>64</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Thread wound around me in a tidy reel, I feed the machine that sews the seam real. What am I?</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>A spool</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>449</v>
+      </c>
+      <c r="B450" t="n">
+        <v>65</v>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Threads stretched tight in a crossing dance, I weave the cloth thread by thread, not by chance. What am I?</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>A loom</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>450</v>
+      </c>
+      <c r="B451" t="n">
+        <v>65</v>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>A furnace of fire where the clay is baked, hardening the pots that the potter made. What am I?</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>A kiln</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/Riddle_Content_Bank.xlsx
+++ b/Riddle_Content_Bank.xlsx
@@ -14048,5700 +14048,5715 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="n">
+      <c r="A302" s="31" t="n">
         <v>301</v>
       </c>
-      <c r="B302" t="n">
+      <c r="B302" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="C302" t="inlineStr">
+      <c r="C302" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr">
+      <c r="D302" s="31" t="inlineStr">
         <is>
           <t>I grip and I pinch with two jaws of steel, bending the wire that won't easily yield. What am I?</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr">
+      <c r="E302" s="31" t="inlineStr">
         <is>
           <t>Pliers</t>
         </is>
       </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
+      <c r="F302" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G302" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H302" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I302" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/e7WbcJesC28</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="n">
+      <c r="A303" s="31" t="n">
         <v>302</v>
       </c>
-      <c r="B303" t="n">
+      <c r="B303" s="31" t="n">
         <v>44</v>
       </c>
-      <c r="C303" t="inlineStr">
+      <c r="C303" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr">
+      <c r="D303" s="31" t="inlineStr">
         <is>
           <t>Struck on my head, I bite into wood or stone, shaving off slivers to leave shapes alone. What am I?</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr">
+      <c r="E303" s="31" t="inlineStr">
         <is>
           <t>A chisel</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G303" t="inlineStr">
+      <c r="F303" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G303" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H303" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I303" s="31" t="inlineStr">
+        <is>
+          <t>https://youtu.be/gDC4hqNIjs8</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="n">
+      <c r="A304" s="31" t="n">
         <v>303</v>
       </c>
-      <c r="B304" t="n">
+      <c r="B304" s="31" t="n">
         <v>44</v>
       </c>
-      <c r="C304" t="inlineStr">
+      <c r="C304" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr">
+      <c r="D304" s="31" t="inlineStr">
         <is>
           <t>Rough on one side, I rub away the old, smoothing the splinters till the surface is bold. What am I?</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr">
+      <c r="E304" s="31" t="inlineStr">
         <is>
           <t>Sandpaper</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
+      <c r="F304" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G304" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="H304" s="31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>https://youtu.be/az4n362gAj0</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="n">
+      <c r="A305" s="31" t="n">
         <v>304</v>
       </c>
-      <c r="B305" t="n">
+      <c r="B305" s="31" t="n">
         <v>44</v>
       </c>
-      <c r="C305" t="inlineStr">
+      <c r="C305" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr">
+      <c r="D305" s="31" t="inlineStr">
         <is>
           <t>A bubble lives in me and floats to the top; I tell you when to build and when to stop. What am I?</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr">
+      <c r="E305" s="31" t="inlineStr">
         <is>
           <t>A spirit level</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
+      <c r="F305" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G305" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H305" t="inlineStr">
+      <c r="H305" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="n">
+      <c r="A306" s="31" t="n">
         <v>305</v>
       </c>
-      <c r="B306" t="n">
+      <c r="B306" s="31" t="n">
         <v>44</v>
       </c>
-      <c r="C306" t="inlineStr">
+      <c r="C306" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr">
+      <c r="D306" s="31" t="inlineStr">
         <is>
           <t>I roll out in inches then snap back inside; how long is it? I'm the one you confide. What am I?</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr">
+      <c r="E306" s="31" t="inlineStr">
         <is>
           <t>A tape measure</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
+      <c r="F306" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G306" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr">
+      <c r="H306" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="n">
+      <c r="A307" s="31" t="n">
         <v>306</v>
       </c>
-      <c r="B307" t="n">
+      <c r="B307" s="31" t="n">
         <v>44</v>
       </c>
-      <c r="C307" t="inlineStr">
+      <c r="C307" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr">
+      <c r="D307" s="31" t="inlineStr">
         <is>
           <t>I hold two pieces in a stubborn embrace while the glue dries slowly into place. What am I?</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr">
+      <c r="E307" s="31" t="inlineStr">
         <is>
           <t>A clamp</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
+      <c r="F307" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G307" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr">
+      <c r="H307" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="n">
+      <c r="A308" s="31" t="n">
         <v>307</v>
       </c>
-      <c r="B308" t="n">
+      <c r="B308" s="31" t="n">
         <v>44</v>
       </c>
-      <c r="C308" t="inlineStr">
+      <c r="C308" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr">
+      <c r="D308" s="31" t="inlineStr">
         <is>
           <t>Heavy and horned, I take every blow; the blacksmith shapes metal on me, you know. What am I?</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr">
+      <c r="E308" s="31" t="inlineStr">
         <is>
           <t>An anvil</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
+      <c r="F308" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G308" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr">
+      <c r="H308" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="n">
+      <c r="A309" s="31" t="n">
         <v>308</v>
       </c>
-      <c r="B309" t="n">
+      <c r="B309" s="31" t="n">
         <v>44</v>
       </c>
-      <c r="C309" t="inlineStr">
+      <c r="C309" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr">
+      <c r="D309" s="31" t="inlineStr">
         <is>
           <t>Step on my shoulder and I bite the ground, lifting the earth in a heap all around. What am I?</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr">
+      <c r="E309" s="31" t="inlineStr">
         <is>
           <t>A shovel</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
+      <c r="F309" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G309" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr">
+      <c r="H309" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="n">
+      <c r="A310" s="31" t="n">
         <v>309</v>
       </c>
-      <c r="B310" t="n">
+      <c r="B310" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="C310" t="inlineStr">
+      <c r="C310" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr">
+      <c r="D310" s="31" t="inlineStr">
         <is>
           <t>With fingers of metal but no hand at all, I gather the leaves when they start to fall. What am I?</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
+      <c r="E310" s="31" t="inlineStr">
         <is>
           <t>A rake</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
+      <c r="F310" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G310" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr">
+      <c r="H310" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="n">
+      <c r="A311" s="31" t="n">
         <v>310</v>
       </c>
-      <c r="B311" t="n">
+      <c r="B311" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="C311" t="inlineStr">
+      <c r="C311" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr">
+      <c r="D311" s="31" t="inlineStr">
         <is>
           <t>One wheel in front and two legs behind, I carry your load of the heavy kind. What am I?</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr">
+      <c r="E311" s="31" t="inlineStr">
         <is>
           <t>A wheelbarrow</t>
         </is>
       </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G311" t="inlineStr">
+      <c r="F311" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G311" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr">
+      <c r="H311" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="n">
+      <c r="A312" s="31" t="n">
         <v>311</v>
       </c>
-      <c r="B312" t="n">
+      <c r="B312" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="C312" t="inlineStr">
+      <c r="C312" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr">
+      <c r="D312" s="31" t="inlineStr">
         <is>
           <t>A wedge on a handle, I swing and I split; the logs fall in two where my sharp edge is hit. What am I?</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr">
+      <c r="E312" s="31" t="inlineStr">
         <is>
           <t>An axe</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
+      <c r="F312" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G312" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr">
+      <c r="H312" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="n">
+      <c r="A313" s="31" t="n">
         <v>312</v>
       </c>
-      <c r="B313" t="n">
+      <c r="B313" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="C313" t="inlineStr">
+      <c r="C313" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr">
+      <c r="D313" s="31" t="inlineStr">
         <is>
           <t>I melt a silver thread to bond two wires tight, hot at my tip with a wisp of white. What am I?</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr">
+      <c r="E313" s="31" t="inlineStr">
         <is>
           <t>A soldering iron</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
+      <c r="F313" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G313" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr">
+      <c r="H313" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="n">
+      <c r="A314" s="31" t="n">
         <v>313</v>
       </c>
-      <c r="B314" t="n">
+      <c r="B314" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="C314" t="inlineStr">
+      <c r="C314" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr">
+      <c r="D314" s="31" t="inlineStr">
         <is>
           <t>Bolted to the bench, I squeeze and I clench, holding your work in an iron pinch. What am I?</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr">
+      <c r="E314" s="31" t="inlineStr">
         <is>
           <t>A vise</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
+      <c r="F314" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G314" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H314" t="inlineStr">
+      <c r="H314" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="n">
+      <c r="A315" s="31" t="n">
         <v>314</v>
       </c>
-      <c r="B315" t="n">
+      <c r="B315" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="C315" t="inlineStr">
+      <c r="C315" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
+      <c r="D315" s="31" t="inlineStr">
         <is>
           <t>A little flat blade for the gardener's hand, I dig the small holes where the seedlings stand. What am I?</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr">
+      <c r="E315" s="31" t="inlineStr">
         <is>
           <t>A trowel</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
+      <c r="F315" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G315" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr">
+      <c r="H315" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="n">
+      <c r="A316" s="31" t="n">
         <v>315</v>
       </c>
-      <c r="B316" t="n">
+      <c r="B316" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="C316" t="inlineStr">
+      <c r="C316" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr">
+      <c r="D316" s="31" t="inlineStr">
         <is>
           <t>Long tines on a pole, I toss the hay high; the farmer lifts bundles as the barn stays dry. What am I?</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr">
+      <c r="E316" s="31" t="inlineStr">
         <is>
           <t>A pitchfork</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
+      <c r="F316" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G316" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr">
+      <c r="H316" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="n">
+      <c r="A317" s="31" t="n">
         <v>316</v>
       </c>
-      <c r="B317" t="n">
+      <c r="B317" s="31" t="n">
         <v>46</v>
       </c>
-      <c r="C317" t="inlineStr">
+      <c r="C317" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr">
+      <c r="D317" s="31" t="inlineStr">
         <is>
           <t>Full of small holes, I let the fine through while keeping the lumps that won't pass for you. What am I?</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr">
+      <c r="E317" s="31" t="inlineStr">
         <is>
           <t>A sieve</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr">
+      <c r="F317" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G317" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr">
+      <c r="H317" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="n">
+      <c r="A318" s="31" t="n">
         <v>317</v>
       </c>
-      <c r="B318" t="n">
+      <c r="B318" s="31" t="n">
         <v>46</v>
       </c>
-      <c r="C318" t="inlineStr">
+      <c r="C318" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
+      <c r="D318" s="31" t="inlineStr">
         <is>
           <t>I shave off the skin in a ribbon so thin, before the potato goes into the tin. What am I?</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr">
+      <c r="E318" s="31" t="inlineStr">
         <is>
           <t>A peeler</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
+      <c r="F318" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G318" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr">
+      <c r="H318" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="n">
+      <c r="A319" s="31" t="n">
         <v>318</v>
       </c>
-      <c r="B319" t="n">
+      <c r="B319" s="31" t="n">
         <v>46</v>
       </c>
-      <c r="C319" t="inlineStr">
+      <c r="C319" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr">
+      <c r="D319" s="31" t="inlineStr">
         <is>
           <t>Two arms and a hinge, I pinch and I grab the hot and the slippery off of the slab. What am I?</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr">
+      <c r="E319" s="31" t="inlineStr">
         <is>
           <t>Tongs</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
+      <c r="F319" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G319" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr">
+      <c r="H319" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="n">
+      <c r="A320" s="31" t="n">
         <v>319</v>
       </c>
-      <c r="B320" t="n">
+      <c r="B320" s="31" t="n">
         <v>46</v>
       </c>
-      <c r="C320" t="inlineStr">
+      <c r="C320" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr">
+      <c r="D320" s="31" t="inlineStr">
         <is>
           <t>Lines on my side say how much to pour; stop at the mark and you'll need no more. What am I?</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr">
+      <c r="E320" s="31" t="inlineStr">
         <is>
           <t>A measuring cup</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
+      <c r="F320" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G320" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr">
+      <c r="H320" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="n">
+      <c r="A321" s="31" t="n">
         <v>320</v>
       </c>
-      <c r="B321" t="n">
+      <c r="B321" s="31" t="n">
         <v>46</v>
       </c>
-      <c r="C321" t="inlineStr">
+      <c r="C321" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr">
+      <c r="D321" s="31" t="inlineStr">
         <is>
           <t>I steep the leaves and I hold the brew, a lid on my top and a spout to pour through. What am I?</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr">
+      <c r="E321" s="31" t="inlineStr">
         <is>
           <t>A teapot</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
+      <c r="F321" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G321" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H321" t="inlineStr">
+      <c r="H321" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="n">
+      <c r="A322" s="31" t="n">
         <v>321</v>
       </c>
-      <c r="B322" t="n">
+      <c r="B322" s="31" t="n">
         <v>46</v>
       </c>
-      <c r="C322" t="inlineStr">
+      <c r="C322" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr">
+      <c r="D322" s="31" t="inlineStr">
         <is>
           <t>Hot stays hot and cold stays cold inside my double-walled hold. What am I?</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr">
+      <c r="E322" s="31" t="inlineStr">
         <is>
           <t>A thermos</t>
         </is>
       </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
+      <c r="F322" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G322" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H322" t="inlineStr">
+      <c r="H322" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="n">
+      <c r="A323" s="31" t="n">
         <v>322</v>
       </c>
-      <c r="B323" t="n">
+      <c r="B323" s="31" t="n">
         <v>46</v>
       </c>
-      <c r="C323" t="inlineStr">
+      <c r="C323" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr">
+      <c r="D323" s="31" t="inlineStr">
         <is>
           <t>I sit on your lap through the whole of the meal, catching the drips that your fingers conceal. What am I?</t>
         </is>
       </c>
-      <c r="E323" t="inlineStr">
+      <c r="E323" s="31" t="inlineStr">
         <is>
           <t>A napkin</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
+      <c r="F323" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G323" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr">
+      <c r="H323" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="n">
+      <c r="A324" s="31" t="n">
         <v>323</v>
       </c>
-      <c r="B324" t="n">
+      <c r="B324" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="C324" t="inlineStr">
+      <c r="C324" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr">
+      <c r="D324" s="31" t="inlineStr">
         <is>
           <t>I plug up the bottle to keep the wine sealed, then pop with a bang when the glass is revealed. What am I?</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr">
+      <c r="E324" s="31" t="inlineStr">
         <is>
           <t>A cork</t>
         </is>
       </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
+      <c r="F324" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G324" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr">
+      <c r="H324" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="n">
+      <c r="A325" s="31" t="n">
         <v>324</v>
       </c>
-      <c r="B325" t="n">
+      <c r="B325" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="C325" t="inlineStr">
+      <c r="C325" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr">
+      <c r="D325" s="31" t="inlineStr">
         <is>
           <t>Glass with a lid that you twist to undo, I keep the jam fresh the whole winter through. What am I?</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr">
+      <c r="E325" s="31" t="inlineStr">
         <is>
           <t>A jar</t>
         </is>
       </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
+      <c r="F325" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G325" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr">
+      <c r="H325" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="n">
+      <c r="A326" s="31" t="n">
         <v>325</v>
       </c>
-      <c r="B326" t="n">
+      <c r="B326" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="C326" t="inlineStr">
+      <c r="C326" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr">
+      <c r="D326" s="31" t="inlineStr">
         <is>
           <t>I slide out and in on a runner or two, holding your socks and your odds and ends too. What am I?</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr">
+      <c r="E326" s="31" t="inlineStr">
         <is>
           <t>A drawer</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
+      <c r="F326" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G326" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr">
+      <c r="H326" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="n">
+      <c r="A327" s="31" t="n">
         <v>326</v>
       </c>
-      <c r="B327" t="n">
+      <c r="B327" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="C327" t="inlineStr">
+      <c r="C327" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr">
+      <c r="D327" s="31" t="inlineStr">
         <is>
           <t>Flat on the wall, I hold up your books; I ask for no thanks for the way the room looks. What am I?</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr">
+      <c r="E327" s="31" t="inlineStr">
         <is>
           <t>A shelf</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
+      <c r="F327" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G327" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H327" t="inlineStr">
+      <c r="H327" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="n">
+      <c r="A328" s="31" t="n">
         <v>327</v>
       </c>
-      <c r="B328" t="n">
+      <c r="B328" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="C328" t="inlineStr">
+      <c r="C328" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr">
+      <c r="D328" s="31" t="inlineStr">
         <is>
           <t>Slung between trees, I sway you to sleep; no legs of my own, just a gentle sweep. What am I?</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr">
+      <c r="E328" s="31" t="inlineStr">
         <is>
           <t>A hammock</t>
         </is>
       </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
+      <c r="F328" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G328" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr">
+      <c r="H328" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="n">
+      <c r="A329" s="31" t="n">
         <v>328</v>
       </c>
-      <c r="B329" t="n">
+      <c r="B329" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="C329" t="inlineStr">
+      <c r="C329" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr">
+      <c r="D329" s="31" t="inlineStr">
         <is>
           <t>I move back and forth but go nowhere at all, soothing the baby or the grandmother tall. What am I?</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr">
+      <c r="E329" s="31" t="inlineStr">
         <is>
           <t>A rocking chair</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
+      <c r="F329" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G329" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr">
+      <c r="H329" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="n">
+      <c r="A330" s="31" t="n">
         <v>329</v>
       </c>
-      <c r="B330" t="n">
+      <c r="B330" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="C330" t="inlineStr">
+      <c r="C330" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr">
+      <c r="D330" s="31" t="inlineStr">
         <is>
           <t>I hang from the ceiling with crystals that gleam, dripping with light like a frozen stream. What am I?</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr">
+      <c r="E330" s="31" t="inlineStr">
         <is>
           <t>A chandelier</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
+      <c r="F330" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G330" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr">
+      <c r="H330" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="n">
+      <c r="A331" s="31" t="n">
         <v>330</v>
       </c>
-      <c r="B331" t="n">
+      <c r="B331" s="31" t="n">
         <v>48</v>
       </c>
-      <c r="C331" t="inlineStr">
+      <c r="C331" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr">
+      <c r="D331" s="31" t="inlineStr">
         <is>
           <t>Ribbed and warm by the wall I stand, hissing out heat when the winter's at hand. What am I?</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr">
+      <c r="E331" s="31" t="inlineStr">
         <is>
           <t>A radiator</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
+      <c r="F331" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G331" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr">
+      <c r="H331" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="n">
+      <c r="A332" s="31" t="n">
         <v>331</v>
       </c>
-      <c r="B332" t="n">
+      <c r="B332" s="31" t="n">
         <v>48</v>
       </c>
-      <c r="C332" t="inlineStr">
+      <c r="C332" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr">
+      <c r="D332" s="31" t="inlineStr">
         <is>
           <t>I open at dawn and I close for the night, keeping the bedroom away from the light. What am I?</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr">
+      <c r="E332" s="31" t="inlineStr">
         <is>
           <t>A curtain</t>
         </is>
       </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
+      <c r="F332" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G332" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr">
+      <c r="H332" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="n">
+      <c r="A333" s="31" t="n">
         <v>332</v>
       </c>
-      <c r="B333" t="n">
+      <c r="B333" s="31" t="n">
         <v>48</v>
       </c>
-      <c r="C333" t="inlineStr">
+      <c r="C333" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr">
+      <c r="D333" s="31" t="inlineStr">
         <is>
           <t>Soft underfoot and spread on the floor, I warm your toes from wall to door. What am I?</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr">
+      <c r="E333" s="31" t="inlineStr">
         <is>
           <t>A carpet</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
+      <c r="F333" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G333" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr">
+      <c r="H333" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="n">
+      <c r="A334" s="31" t="n">
         <v>333</v>
       </c>
-      <c r="B334" t="n">
+      <c r="B334" s="31" t="n">
         <v>48</v>
       </c>
-      <c r="C334" t="inlineStr">
+      <c r="C334" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr">
+      <c r="D334" s="31" t="inlineStr">
         <is>
           <t>I soften the glare of the bulb I surround, a hat for the light that it casts around. What am I?</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr">
+      <c r="E334" s="31" t="inlineStr">
         <is>
           <t>A lampshade</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
+      <c r="F334" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G334" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H334" t="inlineStr">
+      <c r="H334" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="n">
+      <c r="A335" s="31" t="n">
         <v>334</v>
       </c>
-      <c r="B335" t="n">
+      <c r="B335" s="31" t="n">
         <v>48</v>
       </c>
-      <c r="C335" t="inlineStr">
+      <c r="C335" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
+      <c r="D335" s="31" t="inlineStr">
         <is>
           <t>Three legs or four and no back to lean, I'm the shortest seat that you've ever seen. What am I?</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr">
+      <c r="E335" s="31" t="inlineStr">
         <is>
           <t>A stool</t>
         </is>
       </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
+      <c r="F335" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G335" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr">
+      <c r="H335" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="n">
+      <c r="A336" s="31" t="n">
         <v>335</v>
       </c>
-      <c r="B336" t="n">
+      <c r="B336" s="31" t="n">
         <v>48</v>
       </c>
-      <c r="C336" t="inlineStr">
+      <c r="C336" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
+      <c r="D336" s="31" t="inlineStr">
         <is>
           <t>A brim at the front to shade your eyes, I sit on your head beneath sunny skies. What am I?</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr">
+      <c r="E336" s="31" t="inlineStr">
         <is>
           <t>A cap</t>
         </is>
       </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
+      <c r="F336" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G336" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr">
+      <c r="H336" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="n">
+      <c r="A337" s="31" t="n">
         <v>336</v>
       </c>
-      <c r="B337" t="n">
+      <c r="B337" s="31" t="n">
         <v>48</v>
       </c>
-      <c r="C337" t="inlineStr">
+      <c r="C337" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
+      <c r="D337" s="31" t="inlineStr">
         <is>
           <t>A band over the top and a muff on each ear, I keep out the cold when winter is near. What am I?</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr">
+      <c r="E337" s="31" t="inlineStr">
         <is>
           <t>Earmuffs</t>
         </is>
       </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
+      <c r="F337" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G337" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H337" t="inlineStr">
+      <c r="H337" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="n">
+      <c r="A338" s="31" t="n">
         <v>337</v>
       </c>
-      <c r="B338" t="n">
+      <c r="B338" s="31" t="n">
         <v>49</v>
       </c>
-      <c r="C338" t="inlineStr">
+      <c r="C338" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr">
+      <c r="D338" s="31" t="inlineStr">
         <is>
           <t>Criss-crossed and knotted, I hold the shoe tight; undo me too loose and you'll trip in the night. What am I?</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr">
+      <c r="E338" s="31" t="inlineStr">
         <is>
           <t>A shoelace</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
+      <c r="F338" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G338" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H338" t="inlineStr">
+      <c r="H338" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="n">
+      <c r="A339" s="31" t="n">
         <v>338</v>
       </c>
-      <c r="B339" t="n">
+      <c r="B339" s="31" t="n">
         <v>49</v>
       </c>
-      <c r="C339" t="inlineStr">
+      <c r="C339" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr">
+      <c r="D339" s="31" t="inlineStr">
         <is>
           <t>I sit at the collar in a neat little knot, dressing you up for the fancy spot. What am I?</t>
         </is>
       </c>
-      <c r="E339" t="inlineStr">
+      <c r="E339" s="31" t="inlineStr">
         <is>
           <t>A bowtie</t>
         </is>
       </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr">
+      <c r="F339" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G339" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H339" t="inlineStr">
+      <c r="H339" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="n">
+      <c r="A340" s="31" t="n">
         <v>339</v>
       </c>
-      <c r="B340" t="n">
+      <c r="B340" s="31" t="n">
         <v>49</v>
       </c>
-      <c r="C340" t="inlineStr">
+      <c r="C340" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr">
+      <c r="D340" s="31" t="inlineStr">
         <is>
           <t>Metal and prong, I fasten the strap, cinching the belt with a satisfying snap. What am I?</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr">
+      <c r="E340" s="31" t="inlineStr">
         <is>
           <t>A buckle</t>
         </is>
       </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
+      <c r="F340" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G340" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr">
+      <c r="H340" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="n">
+      <c r="A341" s="31" t="n">
         <v>340</v>
       </c>
-      <c r="B341" t="n">
+      <c r="B341" s="31" t="n">
         <v>49</v>
       </c>
-      <c r="C341" t="inlineStr">
+      <c r="C341" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr">
+      <c r="D341" s="31" t="inlineStr">
         <is>
           <t>A circle of beads round the wrist I lie, jingling softly as the hand goes by. What am I?</t>
         </is>
       </c>
-      <c r="E341" t="inlineStr">
+      <c r="E341" s="31" t="inlineStr">
         <is>
           <t>A bracelet</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
+      <c r="F341" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G341" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr">
+      <c r="H341" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="n">
+      <c r="A342" s="31" t="n">
         <v>341</v>
       </c>
-      <c r="B342" t="n">
+      <c r="B342" s="31" t="n">
         <v>49</v>
       </c>
-      <c r="C342" t="inlineStr">
+      <c r="C342" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr">
+      <c r="D342" s="31" t="inlineStr">
         <is>
           <t>Thin and sheer, I cover the face, lifted at last in a moment of grace. What am I?</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr">
+      <c r="E342" s="31" t="inlineStr">
         <is>
           <t>A veil</t>
         </is>
       </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr">
+      <c r="F342" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G342" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H342" t="inlineStr">
+      <c r="H342" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="n">
+      <c r="A343" s="31" t="n">
         <v>342</v>
       </c>
-      <c r="B343" t="n">
+      <c r="B343" s="31" t="n">
         <v>49</v>
       </c>
-      <c r="C343" t="inlineStr">
+      <c r="C343" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr">
+      <c r="D343" s="31" t="inlineStr">
         <is>
           <t>Six-sided rooms in a wall of gold, I store the sweet that the bees have told. What am I?</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr">
+      <c r="E343" s="31" t="inlineStr">
         <is>
           <t>A honeycomb</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr">
+      <c r="F343" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G343" t="inlineStr">
+      <c r="G343" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr">
+      <c r="H343" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="n">
+      <c r="A344" s="31" t="n">
         <v>343</v>
       </c>
-      <c r="B344" t="n">
+      <c r="B344" s="31" t="n">
         <v>49</v>
       </c>
-      <c r="C344" t="inlineStr">
+      <c r="C344" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr">
+      <c r="D344" s="31" t="inlineStr">
         <is>
           <t>Spun in the corner on threads so fine, I catch the fly in a silken line. What am I?</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr">
+      <c r="E344" s="31" t="inlineStr">
         <is>
           <t>A spider's web</t>
         </is>
       </c>
-      <c r="F344" t="inlineStr">
+      <c r="F344" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G344" t="inlineStr">
+      <c r="G344" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr">
+      <c r="H344" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="n">
+      <c r="A345" s="31" t="n">
         <v>344</v>
       </c>
-      <c r="B345" t="n">
+      <c r="B345" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="C345" t="inlineStr">
+      <c r="C345" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr">
+      <c r="D345" s="31" t="inlineStr">
         <is>
           <t>I wrap up a crawler in silk nice and tight; it sleeps and transforms, then takes to flight. What am I?</t>
         </is>
       </c>
-      <c r="E345" t="inlineStr">
+      <c r="E345" s="31" t="inlineStr">
         <is>
           <t>A cocoon</t>
         </is>
       </c>
-      <c r="F345" t="inlineStr">
+      <c r="F345" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G345" t="inlineStr">
+      <c r="G345" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr">
+      <c r="H345" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="n">
+      <c r="A346" s="31" t="n">
         <v>345</v>
       </c>
-      <c r="B346" t="n">
+      <c r="B346" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="C346" t="inlineStr">
+      <c r="C346" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr">
+      <c r="D346" s="31" t="inlineStr">
         <is>
           <t>Woven of twigs in the fork of a tree, I cradle the eggs till they're ready and free. What am I?</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr">
+      <c r="E346" s="31" t="inlineStr">
         <is>
           <t>A nest</t>
         </is>
       </c>
-      <c r="F346" t="inlineStr">
+      <c r="F346" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G346" t="inlineStr">
+      <c r="G346" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr">
+      <c r="H346" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="n">
+      <c r="A347" s="31" t="n">
         <v>346</v>
       </c>
-      <c r="B347" t="n">
+      <c r="B347" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="C347" t="inlineStr">
+      <c r="C347" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr">
+      <c r="D347" s="31" t="inlineStr">
         <is>
           <t>Light as can be, I fall without sound; I helped a bird fly before touching the ground. What am I?</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr">
+      <c r="E347" s="31" t="inlineStr">
         <is>
           <t>A feather</t>
         </is>
       </c>
-      <c r="F347" t="inlineStr">
+      <c r="F347" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr">
+      <c r="G347" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr">
+      <c r="H347" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="n">
+      <c r="A348" s="31" t="n">
         <v>347</v>
       </c>
-      <c r="B348" t="n">
+      <c r="B348" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="C348" t="inlineStr">
+      <c r="C348" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr">
+      <c r="D348" s="31" t="inlineStr">
         <is>
           <t>Branched like a tree on the head of a deer, I'm shed every year and grow back next year. What am I?</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr">
+      <c r="E348" s="31" t="inlineStr">
         <is>
           <t>An antler</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr">
+      <c r="F348" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G348" t="inlineStr">
+      <c r="G348" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr">
+      <c r="H348" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="n">
+      <c r="A349" s="31" t="n">
         <v>348</v>
       </c>
-      <c r="B349" t="n">
+      <c r="B349" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="C349" t="inlineStr">
+      <c r="C349" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr">
+      <c r="D349" s="31" t="inlineStr">
         <is>
           <t>I look like a plant but I'm built by small creatures, a reef full of color with limestone features. What am I?</t>
         </is>
       </c>
-      <c r="E349" t="inlineStr">
+      <c r="E349" s="31" t="inlineStr">
         <is>
           <t>Coral</t>
         </is>
       </c>
-      <c r="F349" t="inlineStr">
+      <c r="F349" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G349" t="inlineStr">
+      <c r="G349" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr">
+      <c r="H349" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="n">
+      <c r="A350" s="31" t="n">
         <v>349</v>
       </c>
-      <c r="B350" t="n">
+      <c r="B350" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="C350" t="inlineStr">
+      <c r="C350" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr">
+      <c r="D350" s="31" t="inlineStr">
         <is>
           <t>I unroll my fronds from a tight little curl, in the shade of the forest I slowly unfurl. What am I?</t>
         </is>
       </c>
-      <c r="E350" t="inlineStr">
+      <c r="E350" s="31" t="inlineStr">
         <is>
           <t>A fern</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr">
+      <c r="F350" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr">
+      <c r="G350" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr">
+      <c r="H350" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="n">
+      <c r="A351" s="31" t="n">
         <v>350</v>
       </c>
-      <c r="B351" t="n">
+      <c r="B351" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="C351" t="inlineStr">
+      <c r="C351" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr">
+      <c r="D351" s="31" t="inlineStr">
         <is>
           <t>I climb up the wall with a grip and a twist, reaching for sunlight I cannot resist. What am I?</t>
         </is>
       </c>
-      <c r="E351" t="inlineStr">
+      <c r="E351" s="31" t="inlineStr">
         <is>
           <t>A vine</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr">
+      <c r="F351" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr">
+      <c r="G351" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr">
+      <c r="H351" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="n">
+      <c r="A352" s="31" t="n">
         <v>351</v>
       </c>
-      <c r="B352" t="n">
+      <c r="B352" s="31" t="n">
         <v>51</v>
       </c>
-      <c r="C352" t="inlineStr">
+      <c r="C352" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
+      <c r="D352" s="31" t="inlineStr">
         <is>
           <t>I blur the whole morning and swallow the hill; you drive through me slowly, the air damp and still. What am I?</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr">
+      <c r="E352" s="31" t="inlineStr">
         <is>
           <t>Fog</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr">
+      <c r="F352" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr">
+      <c r="G352" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr">
+      <c r="H352" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="n">
+      <c r="A353" s="31" t="n">
         <v>352</v>
       </c>
-      <c r="B353" t="n">
+      <c r="B353" s="31" t="n">
         <v>51</v>
       </c>
-      <c r="C353" t="inlineStr">
+      <c r="C353" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr">
+      <c r="D353" s="31" t="inlineStr">
         <is>
           <t>I paint the window in feathers of white, laid down by the cold in the dark of the night. What am I?</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr">
+      <c r="E353" s="31" t="inlineStr">
         <is>
           <t>Frost</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr">
+      <c r="F353" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr">
+      <c r="G353" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr">
+      <c r="H353" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="n">
+      <c r="A354" s="31" t="n">
         <v>353</v>
       </c>
-      <c r="B354" t="n">
+      <c r="B354" s="31" t="n">
         <v>51</v>
       </c>
-      <c r="C354" t="inlineStr">
+      <c r="C354" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr">
+      <c r="D354" s="31" t="inlineStr">
         <is>
           <t>I fall from the storm as a pellet of ice, bouncing on rooftops — not gentle, not nice. What am I?</t>
         </is>
       </c>
-      <c r="E354" t="inlineStr">
+      <c r="E354" s="31" t="inlineStr">
         <is>
           <t>Hail</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr">
+      <c r="F354" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr">
+      <c r="G354" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr">
+      <c r="H354" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="n">
+      <c r="A355" s="31" t="n">
         <v>354</v>
       </c>
-      <c r="B355" t="n">
+      <c r="B355" s="31" t="n">
         <v>51</v>
       </c>
-      <c r="C355" t="inlineStr">
+      <c r="C355" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr">
+      <c r="D355" s="31" t="inlineStr">
         <is>
           <t>On the hot desert road I shimmer like water, a lie of the heat that leads you no farther. What am I?</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr">
+      <c r="E355" s="31" t="inlineStr">
         <is>
           <t>A mirage</t>
         </is>
       </c>
-      <c r="F355" t="inlineStr">
+      <c r="F355" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr">
+      <c r="G355" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H355" t="inlineStr">
+      <c r="H355" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="n">
+      <c r="A356" s="31" t="n">
         <v>355</v>
       </c>
-      <c r="B356" t="n">
+      <c r="B356" s="31" t="n">
         <v>51</v>
       </c>
-      <c r="C356" t="inlineStr">
+      <c r="C356" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr">
+      <c r="D356" s="31" t="inlineStr">
         <is>
           <t>One body slides in front of another, and day turns to dusk as the light they smother. What am I?</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr">
+      <c r="E356" s="31" t="inlineStr">
         <is>
           <t>An eclipse</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr">
+      <c r="F356" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr">
+      <c r="G356" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H356" t="inlineStr">
+      <c r="H356" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="n">
+      <c r="A357" s="31" t="n">
         <v>356</v>
       </c>
-      <c r="B357" t="n">
+      <c r="B357" s="31" t="n">
         <v>51</v>
       </c>
-      <c r="C357" t="inlineStr">
+      <c r="C357" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr">
+      <c r="D357" s="31" t="inlineStr">
         <is>
           <t>A streak in the night as I burn up on high, you make a quick wish as I shoot through the sky. What am I?</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr">
+      <c r="E357" s="31" t="inlineStr">
         <is>
           <t>A meteor</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr">
+      <c r="F357" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G357" t="inlineStr">
+      <c r="G357" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H357" t="inlineStr">
+      <c r="H357" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="n">
+      <c r="A358" s="31" t="n">
         <v>357</v>
       </c>
-      <c r="B358" t="n">
+      <c r="B358" s="31" t="n">
         <v>51</v>
       </c>
-      <c r="C358" t="inlineStr">
+      <c r="C358" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr">
+      <c r="D358" s="31" t="inlineStr">
         <is>
           <t>A whirlpool of billions of stars I hold, a spiral of light in the dark and cold. What am I?</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr">
+      <c r="E358" s="31" t="inlineStr">
         <is>
           <t>A galaxy</t>
         </is>
       </c>
-      <c r="F358" t="inlineStr">
+      <c r="F358" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr">
+      <c r="G358" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H358" t="inlineStr">
+      <c r="H358" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="n">
+      <c r="A359" s="31" t="n">
         <v>358</v>
       </c>
-      <c r="B359" t="n">
+      <c r="B359" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="C359" t="inlineStr">
+      <c r="C359" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr">
+      <c r="D359" s="31" t="inlineStr">
         <is>
           <t>I bead on the grass in the cool of the dawn, tiny and bright, then by noon I am gone. What am I?</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr">
+      <c r="E359" s="31" t="inlineStr">
         <is>
           <t>Dew</t>
         </is>
       </c>
-      <c r="F359" t="inlineStr">
+      <c r="F359" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr">
+      <c r="G359" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H359" t="inlineStr">
+      <c r="H359" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="n">
+      <c r="A360" s="31" t="n">
         <v>359</v>
       </c>
-      <c r="B360" t="n">
+      <c r="B360" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="C360" t="inlineStr">
+      <c r="C360" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr">
+      <c r="D360" s="31" t="inlineStr">
         <is>
           <t>I spin the warm sea into towering walls, with a calm, quiet eye where the stillness falls. What am I?</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr">
+      <c r="E360" s="31" t="inlineStr">
         <is>
           <t>A hurricane</t>
         </is>
       </c>
-      <c r="F360" t="inlineStr">
+      <c r="F360" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr">
+      <c r="G360" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr">
+      <c r="H360" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="n">
+      <c r="A361" s="31" t="n">
         <v>360</v>
       </c>
-      <c r="B361" t="n">
+      <c r="B361" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="C361" t="inlineStr">
+      <c r="C361" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr">
+      <c r="D361" s="31" t="inlineStr">
         <is>
           <t>A tiny curved hair on the rim of the eye, I guard against dust as it floats on by. What am I?</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr">
+      <c r="E361" s="31" t="inlineStr">
         <is>
           <t>An eyelash</t>
         </is>
       </c>
-      <c r="F361" t="inlineStr">
+      <c r="F361" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr">
+      <c r="G361" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr">
+      <c r="H361" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="n">
+      <c r="A362" s="31" t="n">
         <v>361</v>
       </c>
-      <c r="B362" t="n">
+      <c r="B362" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="C362" t="inlineStr">
+      <c r="C362" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr">
+      <c r="D362" s="31" t="inlineStr">
         <is>
           <t>I bend in the finger and crack when you press, a hinge in the hand, more or less. What am I?</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr">
+      <c r="E362" s="31" t="inlineStr">
         <is>
           <t>A knuckle</t>
         </is>
       </c>
-      <c r="F362" t="inlineStr">
+      <c r="F362" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr">
+      <c r="G362" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H362" t="inlineStr">
+      <c r="H362" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="n">
+      <c r="A363" s="31" t="n">
         <v>362</v>
       </c>
-      <c r="B363" t="n">
+      <c r="B363" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="C363" t="inlineStr">
+      <c r="C363" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr">
+      <c r="D363" s="31" t="inlineStr">
         <is>
           <t>A small happy dent in the cheek I appear, only when smiling or grinning ear to ear. What am I?</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr">
+      <c r="E363" s="31" t="inlineStr">
         <is>
           <t>A dimple</t>
         </is>
       </c>
-      <c r="F363" t="inlineStr">
+      <c r="F363" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G363" t="inlineStr">
+      <c r="G363" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H363" t="inlineStr">
+      <c r="H363" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="n">
+      <c r="A364" s="31" t="n">
         <v>363</v>
       </c>
-      <c r="B364" t="n">
+      <c r="B364" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="C364" t="inlineStr">
+      <c r="C364" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr">
+      <c r="D364" s="31" t="inlineStr">
         <is>
           <t>A speck of brown the sun brings out, scattered on noses and cheeks about. What am I?</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr">
+      <c r="E364" s="31" t="inlineStr">
         <is>
           <t>A freckle</t>
         </is>
       </c>
-      <c r="F364" t="inlineStr">
+      <c r="F364" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr">
+      <c r="G364" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr">
+      <c r="H364" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="n">
+      <c r="A365" s="31" t="n">
         <v>364</v>
       </c>
-      <c r="B365" t="n">
+      <c r="B365" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="C365" t="inlineStr">
+      <c r="C365" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr">
+      <c r="D365" s="31" t="inlineStr">
         <is>
           <t>A tight little skin deep inside the ear, I quiver with sound so that you can hear. What am I?</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr">
+      <c r="E365" s="31" t="inlineStr">
         <is>
           <t>An eardrum</t>
         </is>
       </c>
-      <c r="F365" t="inlineStr">
+      <c r="F365" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr">
+      <c r="G365" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr">
+      <c r="H365" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="n">
+      <c r="A366" s="31" t="n">
         <v>365</v>
       </c>
-      <c r="B366" t="n">
+      <c r="B366" s="31" t="n">
         <v>53</v>
       </c>
-      <c r="C366" t="inlineStr">
+      <c r="C366" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr">
+      <c r="D366" s="31" t="inlineStr">
         <is>
           <t>I spread without legs and I grow as I go, started by one, soon everyone's in the know. What am I?</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr">
+      <c r="E366" s="31" t="inlineStr">
         <is>
           <t>A rumor</t>
         </is>
       </c>
-      <c r="F366" t="inlineStr">
+      <c r="F366" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr">
+      <c r="G366" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr">
+      <c r="H366" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="n">
+      <c r="A367" s="31" t="n">
         <v>366</v>
       </c>
-      <c r="B367" t="n">
+      <c r="B367" s="31" t="n">
         <v>53</v>
       </c>
-      <c r="C367" t="inlineStr">
+      <c r="C367" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr">
+      <c r="D367" s="31" t="inlineStr">
         <is>
           <t>Blow out the candles or watch a star fall, say me in silence — don't tell them at all. What am I?</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr">
+      <c r="E367" s="31" t="inlineStr">
         <is>
           <t>A wish</t>
         </is>
       </c>
-      <c r="F367" t="inlineStr">
+      <c r="F367" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G367" t="inlineStr">
+      <c r="G367" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H367" t="inlineStr">
+      <c r="H367" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="n">
+      <c r="A368" s="31" t="n">
         <v>367</v>
       </c>
-      <c r="B368" t="n">
+      <c r="B368" s="31" t="n">
         <v>53</v>
       </c>
-      <c r="C368" t="inlineStr">
+      <c r="C368" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr">
+      <c r="D368" s="31" t="inlineStr">
         <is>
           <t>I'm what you run out of while stuck in a queue, the virtue of waiting till something comes through. What am I?</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr">
+      <c r="E368" s="31" t="inlineStr">
         <is>
           <t>Patience</t>
         </is>
       </c>
-      <c r="F368" t="inlineStr">
+      <c r="F368" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr">
+      <c r="G368" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr">
+      <c r="H368" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="n">
+      <c r="A369" s="31" t="n">
         <v>368</v>
       </c>
-      <c r="B369" t="n">
+      <c r="B369" s="31" t="n">
         <v>53</v>
       </c>
-      <c r="C369" t="inlineStr">
+      <c r="C369" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr">
+      <c r="D369" s="31" t="inlineStr">
         <is>
           <t>Held in the heart long after the slight, I'm heavy to carry both day and night. What am I?</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr">
+      <c r="E369" s="31" t="inlineStr">
         <is>
           <t>A grudge</t>
         </is>
       </c>
-      <c r="F369" t="inlineStr">
+      <c r="F369" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr">
+      <c r="G369" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H369" t="inlineStr">
+      <c r="H369" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="n">
+      <c r="A370" s="31" t="n">
         <v>369</v>
       </c>
-      <c r="B370" t="n">
+      <c r="B370" s="31" t="n">
         <v>53</v>
       </c>
-      <c r="C370" t="inlineStr">
+      <c r="C370" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr">
+      <c r="D370" s="31" t="inlineStr">
         <is>
           <t>The hands point straight up when the old day is dead, and a brand-new one starts while you're still in bed. What am I?</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr">
+      <c r="E370" s="31" t="inlineStr">
         <is>
           <t>Midnight</t>
         </is>
       </c>
-      <c r="F370" t="inlineStr">
+      <c r="F370" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr">
+      <c r="G370" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr">
+      <c r="H370" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="n">
+      <c r="A371" s="31" t="n">
         <v>370</v>
       </c>
-      <c r="B371" t="n">
+      <c r="B371" s="31" t="n">
         <v>53</v>
       </c>
-      <c r="C371" t="inlineStr">
+      <c r="C371" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr">
+      <c r="D371" s="31" t="inlineStr">
         <is>
           <t>Ten trips of the earth all the way round the sun, I'm counted in tens when they're finally done. What am I?</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr">
+      <c r="E371" s="31" t="inlineStr">
         <is>
           <t>A decade</t>
         </is>
       </c>
-      <c r="F371" t="inlineStr">
+      <c r="F371" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr">
+      <c r="G371" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H371" t="inlineStr">
+      <c r="H371" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="n">
+      <c r="A372" s="31" t="n">
         <v>371</v>
       </c>
-      <c r="B372" t="n">
+      <c r="B372" s="31" t="n">
         <v>53</v>
       </c>
-      <c r="C372" t="inlineStr">
+      <c r="C372" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
+      <c r="D372" s="31" t="inlineStr">
         <is>
           <t>Once every four I add one more day, giving February its extra stay. What am I?</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr">
+      <c r="E372" s="31" t="inlineStr">
         <is>
           <t>A leap year</t>
         </is>
       </c>
-      <c r="F372" t="inlineStr">
+      <c r="F372" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr">
+      <c r="G372" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr">
+      <c r="H372" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="n">
+      <c r="A373" s="31" t="n">
         <v>372</v>
       </c>
-      <c r="B373" t="n">
+      <c r="B373" s="31" t="n">
         <v>54</v>
       </c>
-      <c r="C373" t="inlineStr">
+      <c r="C373" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr">
+      <c r="D373" s="31" t="inlineStr">
         <is>
           <t>The in-between time, not day and not night, when the sun's gone to bed but there's still a faint light. What am I?</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr">
+      <c r="E373" s="31" t="inlineStr">
         <is>
           <t>Twilight</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr">
+      <c r="F373" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr">
+      <c r="G373" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr">
+      <c r="H373" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="n">
+      <c r="A374" s="31" t="n">
         <v>373</v>
       </c>
-      <c r="B374" t="n">
+      <c r="B374" s="31" t="n">
         <v>54</v>
       </c>
-      <c r="C374" t="inlineStr">
+      <c r="C374" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr">
+      <c r="D374" s="31" t="inlineStr">
         <is>
           <t>I crack open the sky at the edge of the east, the first light of morning for man and for beast. What am I?</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr">
+      <c r="E374" s="31" t="inlineStr">
         <is>
           <t>Dawn</t>
         </is>
       </c>
-      <c r="F374" t="inlineStr">
+      <c r="F374" s="31" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr">
+      <c r="G374" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H374" t="inlineStr">
+      <c r="H374" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="n">
+      <c r="A375" s="31" t="n">
         <v>374</v>
       </c>
-      <c r="B375" t="n">
+      <c r="B375" s="31" t="n">
         <v>54</v>
       </c>
-      <c r="C375" t="inlineStr">
+      <c r="C375" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr">
+      <c r="D375" s="31" t="inlineStr">
         <is>
           <t>Two brass plates that crash with a clang, the loudest I speak with a shimmering bang. What am I?</t>
         </is>
       </c>
-      <c r="E375" t="inlineStr">
+      <c r="E375" s="31" t="inlineStr">
         <is>
           <t>A cymbal</t>
         </is>
       </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr">
+      <c r="F375" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G375" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H375" t="inlineStr">
+      <c r="H375" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="n">
+      <c r="A376" s="31" t="n">
         <v>375</v>
       </c>
-      <c r="B376" t="n">
+      <c r="B376" s="31" t="n">
         <v>54</v>
       </c>
-      <c r="C376" t="inlineStr">
+      <c r="C376" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr">
+      <c r="D376" s="31" t="inlineStr">
         <is>
           <t>A bag full of air and some pipes in a row, I drone and I squeal when the piper lets go. What am I?</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr">
+      <c r="E376" s="31" t="inlineStr">
         <is>
           <t>Bagpipes</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G376" t="inlineStr">
+      <c r="F376" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G376" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H376" t="inlineStr">
+      <c r="H376" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="n">
+      <c r="A377" s="31" t="n">
         <v>376</v>
       </c>
-      <c r="B377" t="n">
+      <c r="B377" s="31" t="n">
         <v>54</v>
       </c>
-      <c r="C377" t="inlineStr">
+      <c r="C377" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr">
+      <c r="D377" s="31" t="inlineStr">
         <is>
           <t>Round like a drum with some strings on my face, I twang out a tune at a bluegrass pace. What am I?</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr">
+      <c r="E377" s="31" t="inlineStr">
         <is>
           <t>A banjo</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G377" t="inlineStr">
+      <c r="F377" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G377" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
+      <c r="H377" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="n">
+      <c r="A378" s="31" t="n">
         <v>377</v>
       </c>
-      <c r="B378" t="n">
+      <c r="B378" s="31" t="n">
         <v>54</v>
       </c>
-      <c r="C378" t="inlineStr">
+      <c r="C378" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr">
+      <c r="D378" s="31" t="inlineStr">
         <is>
           <t>Taller than a fiddle, I rest on the floor, bowed between knees for a deep, rich roar. What am I?</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr">
+      <c r="E378" s="31" t="inlineStr">
         <is>
           <t>A cello</t>
         </is>
       </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G378" t="inlineStr">
+      <c r="F378" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G378" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H378" t="inlineStr">
+      <c r="H378" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="n">
+      <c r="A379" s="31" t="n">
         <v>378</v>
       </c>
-      <c r="B379" t="n">
+      <c r="B379" s="31" t="n">
         <v>54</v>
       </c>
-      <c r="C379" t="inlineStr">
+      <c r="C379" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr">
+      <c r="D379" s="31" t="inlineStr">
         <is>
           <t>A tube of black wood with keys down my side, I sing with a reed when the breath is applied. What am I?</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr">
+      <c r="E379" s="31" t="inlineStr">
         <is>
           <t>A clarinet</t>
         </is>
       </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G379" t="inlineStr">
+      <c r="F379" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G379" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr">
+      <c r="H379" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="380">
-      <c r="A380" t="n">
+      <c r="A380" s="31" t="n">
         <v>379</v>
       </c>
-      <c r="B380" t="n">
+      <c r="B380" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="C380" t="inlineStr">
+      <c r="C380" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr">
+      <c r="D380" s="31" t="inlineStr">
         <is>
           <t>Shake me in pairs and I rattle and hiss, filled up with beads for a Latin bliss. What am I?</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr">
+      <c r="E380" s="31" t="inlineStr">
         <is>
           <t>Maracas</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G380" t="inlineStr">
+      <c r="F380" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G380" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr">
+      <c r="H380" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="381">
-      <c r="A381" t="n">
+      <c r="A381" s="31" t="n">
         <v>380</v>
       </c>
-      <c r="B381" t="n">
+      <c r="B381" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="C381" t="inlineStr">
+      <c r="C381" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr">
+      <c r="D381" s="31" t="inlineStr">
         <is>
           <t>Dots on five lines tell the player what's next; I'm the song written down, a musical text. What am I?</t>
         </is>
       </c>
-      <c r="E381" t="inlineStr">
+      <c r="E381" s="31" t="inlineStr">
         <is>
           <t>Sheet music</t>
         </is>
       </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G381" t="inlineStr">
+      <c r="F381" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G381" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr">
+      <c r="H381" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="n">
+      <c r="A382" s="31" t="n">
         <v>381</v>
       </c>
-      <c r="B382" t="n">
+      <c r="B382" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="C382" t="inlineStr">
+      <c r="C382" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr">
+      <c r="D382" s="31" t="inlineStr">
         <is>
           <t>I follow the star on the darkened stage, a circle of brightness wherever they engage. What am I?</t>
         </is>
       </c>
-      <c r="E382" t="inlineStr">
+      <c r="E382" s="31" t="inlineStr">
         <is>
           <t>A spotlight</t>
         </is>
       </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G382" t="inlineStr">
+      <c r="F382" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G382" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H382" t="inlineStr">
+      <c r="H382" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="n">
+      <c r="A383" s="31" t="n">
         <v>382</v>
       </c>
-      <c r="B383" t="n">
+      <c r="B383" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="C383" t="inlineStr">
+      <c r="C383" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr">
+      <c r="D383" s="31" t="inlineStr">
         <is>
           <t>Three-legged stand where the canvas goes, I hold up the painting while the picture grows. What am I?</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr">
+      <c r="E383" s="31" t="inlineStr">
         <is>
           <t>An easel</t>
         </is>
       </c>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G383" t="inlineStr">
+      <c r="F383" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G383" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H383" t="inlineStr">
+      <c r="H383" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="n">
+      <c r="A384" s="31" t="n">
         <v>383</v>
       </c>
-      <c r="B384" t="n">
+      <c r="B384" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="C384" t="inlineStr">
+      <c r="C384" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr">
+      <c r="D384" s="31" t="inlineStr">
         <is>
           <t>Dip me in color and sweep me around, I leave strokes of beauty without any sound. What am I?</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr">
+      <c r="E384" s="31" t="inlineStr">
         <is>
           <t>A paintbrush</t>
         </is>
       </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G384" t="inlineStr">
+      <c r="F384" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G384" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H384" t="inlineStr">
+      <c r="H384" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="n">
+      <c r="A385" s="31" t="n">
         <v>384</v>
       </c>
-      <c r="B385" t="n">
+      <c r="B385" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="C385" t="inlineStr">
+      <c r="C385" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr">
+      <c r="D385" s="31" t="inlineStr">
         <is>
           <t>A little flat tile with spots in two halves; I fall in a line that collapses in halves. What am I?</t>
         </is>
       </c>
-      <c r="E385" t="inlineStr">
+      <c r="E385" s="31" t="inlineStr">
         <is>
           <t>A domino</t>
         </is>
       </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G385" t="inlineStr">
+      <c r="F385" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G385" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H385" t="inlineStr">
+      <c r="H385" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="n">
+      <c r="A386" s="31" t="n">
         <v>385</v>
       </c>
-      <c r="B386" t="n">
+      <c r="B386" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="C386" t="inlineStr">
+      <c r="C386" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr">
+      <c r="D386" s="31" t="inlineStr">
         <is>
           <t>Gold and gleaming, I crown the best, lifted up high above all the rest. What am I?</t>
         </is>
       </c>
-      <c r="E386" t="inlineStr">
+      <c r="E386" s="31" t="inlineStr">
         <is>
           <t>A trophy</t>
         </is>
       </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G386" t="inlineStr">
+      <c r="F386" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G386" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H386" t="inlineStr">
+      <c r="H386" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="n">
+      <c r="A387" s="31" t="n">
         <v>386</v>
       </c>
-      <c r="B387" t="n">
+      <c r="B387" s="31" t="n">
         <v>56</v>
       </c>
-      <c r="C387" t="inlineStr">
+      <c r="C387" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr">
+      <c r="D387" s="31" t="inlineStr">
         <is>
           <t>I stand in the lane for the runner to clear; knock me down and the judges will jeer. What am I?</t>
         </is>
       </c>
-      <c r="E387" t="inlineStr">
+      <c r="E387" s="31" t="inlineStr">
         <is>
           <t>A hurdle</t>
         </is>
       </c>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G387" t="inlineStr">
+      <c r="F387" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G387" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H387" t="inlineStr">
+      <c r="H387" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="n">
+      <c r="A388" s="31" t="n">
         <v>387</v>
       </c>
-      <c r="B388" t="n">
+      <c r="B388" s="31" t="n">
         <v>56</v>
       </c>
-      <c r="C388" t="inlineStr">
+      <c r="C388" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr">
+      <c r="D388" s="31" t="inlineStr">
         <is>
           <t>A circle of numbers in red and in green, aim for my center — the best you've seen. What am I?</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr">
+      <c r="E388" s="31" t="inlineStr">
         <is>
           <t>A dartboard</t>
         </is>
       </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G388" t="inlineStr">
+      <c r="F388" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G388" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr">
+      <c r="H388" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="n">
+      <c r="A389" s="31" t="n">
         <v>388</v>
       </c>
-      <c r="B389" t="n">
+      <c r="B389" s="31" t="n">
         <v>56</v>
       </c>
-      <c r="C389" t="inlineStr">
+      <c r="C389" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr">
+      <c r="D389" s="31" t="inlineStr">
         <is>
           <t>Down the string I drop then climb back to the top, with a flick of the wrist I just won't stop. What am I?</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr">
+      <c r="E389" s="31" t="inlineStr">
         <is>
           <t>A yo-yo</t>
         </is>
       </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G389" t="inlineStr">
+      <c r="F389" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G389" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H389" t="inlineStr">
+      <c r="H389" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="n">
+      <c r="A390" s="31" t="n">
         <v>389</v>
       </c>
-      <c r="B390" t="n">
+      <c r="B390" s="31" t="n">
         <v>56</v>
       </c>
-      <c r="C390" t="inlineStr">
+      <c r="C390" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr">
+      <c r="D390" s="31" t="inlineStr">
         <is>
           <t>A flying disc you fling through the air; the dog runs to catch me, then brings me back there. What am I?</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr">
+      <c r="E390" s="31" t="inlineStr">
         <is>
           <t>A frisbee</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G390" t="inlineStr">
+      <c r="F390" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G390" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr">
+      <c r="H390" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="n">
+      <c r="A391" s="31" t="n">
         <v>390</v>
       </c>
-      <c r="B391" t="n">
+      <c r="B391" s="31" t="n">
         <v>56</v>
       </c>
-      <c r="C391" t="inlineStr">
+      <c r="C391" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr">
+      <c r="D391" s="31" t="inlineStr">
         <is>
           <t>Up goes one end as the other comes down; take turns in the air at the edge of the town. What am I?</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr">
+      <c r="E391" s="31" t="inlineStr">
         <is>
           <t>A seesaw</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G391" t="inlineStr">
+      <c r="F391" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G391" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr">
+      <c r="H391" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="n">
+      <c r="A392" s="31" t="n">
         <v>391</v>
       </c>
-      <c r="B392" t="n">
+      <c r="B392" s="31" t="n">
         <v>56</v>
       </c>
-      <c r="C392" t="inlineStr">
+      <c r="C392" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr">
+      <c r="D392" s="31" t="inlineStr">
         <is>
           <t>A small glass sphere with a swirl inside, I roll on the ground where the children bide. What am I?</t>
         </is>
       </c>
-      <c r="E392" t="inlineStr">
+      <c r="E392" s="31" t="inlineStr">
         <is>
           <t>A marble</t>
         </is>
       </c>
-      <c r="F392" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G392" t="inlineStr">
+      <c r="F392" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G392" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr">
+      <c r="H392" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="n">
+      <c r="A393" s="31" t="n">
         <v>392</v>
       </c>
-      <c r="B393" t="n">
+      <c r="B393" s="31" t="n">
         <v>56</v>
       </c>
-      <c r="C393" t="inlineStr">
+      <c r="C393" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr">
+      <c r="D393" s="31" t="inlineStr">
         <is>
           <t>A thousand small pieces that lock into one; finish my picture and the challenge is done. What am I?</t>
         </is>
       </c>
-      <c r="E393" t="inlineStr">
+      <c r="E393" s="31" t="inlineStr">
         <is>
           <t>A jigsaw puzzle</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G393" t="inlineStr">
+      <c r="F393" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G393" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H393" t="inlineStr">
+      <c r="H393" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="n">
+      <c r="A394" s="31" t="n">
         <v>393</v>
       </c>
-      <c r="B394" t="n">
+      <c r="B394" s="31" t="n">
         <v>57</v>
       </c>
-      <c r="C394" t="inlineStr">
+      <c r="C394" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr">
+      <c r="D394" s="31" t="inlineStr">
         <is>
           <t>Walls upon walls with a path in between; find your way out of my tangled green. What am I?</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr">
+      <c r="E394" s="31" t="inlineStr">
         <is>
           <t>A maze</t>
         </is>
       </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G394" t="inlineStr">
+      <c r="F394" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G394" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr">
+      <c r="H394" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="n">
+      <c r="A395" s="31" t="n">
         <v>394</v>
       </c>
-      <c r="B395" t="n">
+      <c r="B395" s="31" t="n">
         <v>57</v>
       </c>
-      <c r="C395" t="inlineStr">
+      <c r="C395" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr">
+      <c r="D395" s="31" t="inlineStr">
         <is>
           <t>At the back of the boat I swing left and right, steering the vessel through day and night. What am I?</t>
         </is>
       </c>
-      <c r="E395" t="inlineStr">
+      <c r="E395" s="31" t="inlineStr">
         <is>
           <t>A rudder</t>
         </is>
       </c>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G395" t="inlineStr">
+      <c r="F395" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G395" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr">
+      <c r="H395" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="n">
+      <c r="A396" s="31" t="n">
         <v>395</v>
       </c>
-      <c r="B396" t="n">
+      <c r="B396" s="31" t="n">
         <v>57</v>
       </c>
-      <c r="C396" t="inlineStr">
+      <c r="C396" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr">
+      <c r="D396" s="31" t="inlineStr">
         <is>
           <t>I spin at the front and I pull the plane, blades in a blur through the sky I sustain. What am I?</t>
         </is>
       </c>
-      <c r="E396" t="inlineStr">
+      <c r="E396" s="31" t="inlineStr">
         <is>
           <t>A propeller</t>
         </is>
       </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G396" t="inlineStr">
+      <c r="F396" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G396" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr">
+      <c r="H396" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="n">
+      <c r="A397" s="31" t="n">
         <v>396</v>
       </c>
-      <c r="B397" t="n">
+      <c r="B397" s="31" t="n">
         <v>57</v>
       </c>
-      <c r="C397" t="inlineStr">
+      <c r="C397" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr">
+      <c r="D397" s="31" t="inlineStr">
         <is>
           <t>Pointed at both ends, I glide on the lake; paddle me forward for the journey I make. What am I?</t>
         </is>
       </c>
-      <c r="E397" t="inlineStr">
+      <c r="E397" s="31" t="inlineStr">
         <is>
           <t>A canoe</t>
         </is>
       </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G397" t="inlineStr">
+      <c r="F397" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G397" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr">
+      <c r="H397" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="n">
+      <c r="A398" s="31" t="n">
         <v>397</v>
       </c>
-      <c r="B398" t="n">
+      <c r="B398" s="31" t="n">
         <v>57</v>
       </c>
-      <c r="C398" t="inlineStr">
+      <c r="C398" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr">
+      <c r="D398" s="31" t="inlineStr">
         <is>
           <t>No wheels at all, I slide down the snow, carrying children to the valley below. What am I?</t>
         </is>
       </c>
-      <c r="E398" t="inlineStr">
+      <c r="E398" s="31" t="inlineStr">
         <is>
           <t>A sled</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G398" t="inlineStr">
+      <c r="F398" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G398" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H398" t="inlineStr">
+      <c r="H398" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="n">
+      <c r="A399" s="31" t="n">
         <v>398</v>
       </c>
-      <c r="B399" t="n">
+      <c r="B399" s="31" t="n">
         <v>57</v>
       </c>
-      <c r="C399" t="inlineStr">
+      <c r="C399" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr">
+      <c r="D399" s="31" t="inlineStr">
         <is>
           <t>I dangle from a wire up the mountainside, swaying gently on my airborne ride. What am I?</t>
         </is>
       </c>
-      <c r="E399" t="inlineStr">
+      <c r="E399" s="31" t="inlineStr">
         <is>
           <t>A cable car</t>
         </is>
       </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G399" t="inlineStr">
+      <c r="F399" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G399" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H399" t="inlineStr">
+      <c r="H399" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="n">
+      <c r="A400" s="31" t="n">
         <v>399</v>
       </c>
-      <c r="B400" t="n">
+      <c r="B400" s="31" t="n">
         <v>57</v>
       </c>
-      <c r="C400" t="inlineStr">
+      <c r="C400" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr">
+      <c r="D400" s="31" t="inlineStr">
         <is>
           <t>A basket below and a flame burning bright, I lift off the ground on a column of light. What am I?</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr">
+      <c r="E400" s="31" t="inlineStr">
         <is>
           <t>A hot-air balloon</t>
         </is>
       </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G400" t="inlineStr">
+      <c r="F400" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G400" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr">
+      <c r="H400" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="n">
+      <c r="A401" s="31" t="n">
         <v>400</v>
       </c>
-      <c r="B401" t="n">
+      <c r="B401" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="C401" t="inlineStr">
+      <c r="C401" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr">
+      <c r="D401" s="31" t="inlineStr">
         <is>
           <t>Bright orange and ready when the ship goes down, I carry the sailors so they do not drown. What am I?</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr">
+      <c r="E401" s="31" t="inlineStr">
         <is>
           <t>A lifeboat</t>
         </is>
       </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G401" t="inlineStr">
+      <c r="F401" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G401" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H401" t="inlineStr">
+      <c r="H401" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="n">
+      <c r="A402" s="31" t="n">
         <v>401</v>
       </c>
-      <c r="B402" t="n">
+      <c r="B402" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="C402" t="inlineStr">
+      <c r="C402" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr">
+      <c r="D402" s="31" t="inlineStr">
         <is>
           <t>A giant garage where the aircraft sleep, I shelter the planes that the airlines keep. What am I?</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr">
+      <c r="E402" s="31" t="inlineStr">
         <is>
           <t>A hangar</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G402" t="inlineStr">
+      <c r="F402" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G402" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H402" t="inlineStr">
+      <c r="H402" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="n">
+      <c r="A403" s="31" t="n">
         <v>402</v>
       </c>
-      <c r="B403" t="n">
+      <c r="B403" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="C403" t="inlineStr">
+      <c r="C403" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr">
+      <c r="D403" s="31" t="inlineStr">
         <is>
           <t>Four spinning rotors, I hover and fly, taking your photos from up in the sky. What am I?</t>
         </is>
       </c>
-      <c r="E403" t="inlineStr">
+      <c r="E403" s="31" t="inlineStr">
         <is>
           <t>A drone</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr">
+      <c r="F403" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr">
+      <c r="G403" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H403" t="inlineStr">
+      <c r="H403" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="n">
+      <c r="A404" s="31" t="n">
         <v>403</v>
       </c>
-      <c r="B404" t="n">
+      <c r="B404" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="C404" t="inlineStr">
+      <c r="C404" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr">
+      <c r="D404" s="31" t="inlineStr">
         <is>
           <t>A pen with no ink for the screen of your tablet, I draw and I tap without any gadget. What am I?</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr">
+      <c r="E404" s="31" t="inlineStr">
         <is>
           <t>A stylus</t>
         </is>
       </c>
-      <c r="F404" t="inlineStr">
+      <c r="F404" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr">
+      <c r="G404" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr">
+      <c r="H404" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="n">
+      <c r="A405" s="31" t="n">
         <v>404</v>
       </c>
-      <c r="B405" t="n">
+      <c r="B405" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="C405" t="inlineStr">
+      <c r="C405" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr">
+      <c r="D405" s="31" t="inlineStr">
         <is>
           <t>Charged up and ready, I ride in your bag, topping your phone when its battery sags. What am I?</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr">
+      <c r="E405" s="31" t="inlineStr">
         <is>
           <t>A power bank</t>
         </is>
       </c>
-      <c r="F405" t="inlineStr">
+      <c r="F405" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr">
+      <c r="G405" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H405" t="inlineStr">
+      <c r="H405" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="n">
+      <c r="A406" s="31" t="n">
         <v>405</v>
       </c>
-      <c r="B406" t="n">
+      <c r="B406" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="C406" t="inlineStr">
+      <c r="C406" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr">
+      <c r="D406" s="31" t="inlineStr">
         <is>
           <t>Prove you're no robot — I ask you to squint, picking the buses or the blurry print. What am I?</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr">
+      <c r="E406" s="31" t="inlineStr">
         <is>
           <t>A captcha</t>
         </is>
       </c>
-      <c r="F406" t="inlineStr">
+      <c r="F406" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr">
+      <c r="G406" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H406" t="inlineStr">
+      <c r="H406" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="n">
+      <c r="A407" s="31" t="n">
         <v>406</v>
       </c>
-      <c r="B407" t="n">
+      <c r="B407" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="C407" t="inlineStr">
+      <c r="C407" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr">
+      <c r="D407" s="31" t="inlineStr">
         <is>
           <t>An audio show you can play on the go, episodes streaming wherever you go. What am I?</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr">
+      <c r="E407" s="31" t="inlineStr">
         <is>
           <t>A podcast</t>
         </is>
       </c>
-      <c r="F407" t="inlineStr">
+      <c r="F407" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr">
+      <c r="G407" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H407" t="inlineStr">
+      <c r="H407" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="n">
+      <c r="A408" s="31" t="n">
         <v>407</v>
       </c>
-      <c r="B408" t="n">
+      <c r="B408" s="31" t="n">
         <v>59</v>
       </c>
-      <c r="C408" t="inlineStr">
+      <c r="C408" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr">
+      <c r="D408" s="31" t="inlineStr">
         <is>
           <t>A tiny loop that plays without sound, the same little motion going round and round. What am I?</t>
         </is>
       </c>
-      <c r="E408" t="inlineStr">
+      <c r="E408" s="31" t="inlineStr">
         <is>
           <t>A GIF</t>
         </is>
       </c>
-      <c r="F408" t="inlineStr">
+      <c r="F408" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr">
+      <c r="G408" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H408" t="inlineStr">
+      <c r="H408" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="n">
+      <c r="A409" s="31" t="n">
         <v>408</v>
       </c>
-      <c r="B409" t="n">
+      <c r="B409" s="31" t="n">
         <v>59</v>
       </c>
-      <c r="C409" t="inlineStr">
+      <c r="C409" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr">
+      <c r="D409" s="31" t="inlineStr">
         <is>
           <t>Slipped between pages or saved in a tab, I remember the spot that you want to grab. What am I?</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr">
+      <c r="E409" s="31" t="inlineStr">
         <is>
           <t>A bookmark</t>
         </is>
       </c>
-      <c r="F409" t="inlineStr">
+      <c r="F409" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G409" t="inlineStr">
+      <c r="G409" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H409" t="inlineStr">
+      <c r="H409" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="n">
+      <c r="A410" s="31" t="n">
         <v>409</v>
       </c>
-      <c r="B410" t="n">
+      <c r="B410" s="31" t="n">
         <v>59</v>
       </c>
-      <c r="C410" t="inlineStr">
+      <c r="C410" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr">
+      <c r="D410" s="31" t="inlineStr">
         <is>
           <t>I shine a thin light down the page in a sweep, turning your paper to a file you keep. What am I?</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr">
+      <c r="E410" s="31" t="inlineStr">
         <is>
           <t>A scanner</t>
         </is>
       </c>
-      <c r="F410" t="inlineStr">
+      <c r="F410" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr">
+      <c r="G410" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H410" t="inlineStr">
+      <c r="H410" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="n">
+      <c r="A411" s="31" t="n">
         <v>410</v>
       </c>
-      <c r="B411" t="n">
+      <c r="B411" s="31" t="n">
         <v>59</v>
       </c>
-      <c r="C411" t="inlineStr">
+      <c r="C411" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr">
+      <c r="D411" s="31" t="inlineStr">
         <is>
           <t>I spin in your tower and remember it all, your files and your photos both big and small. What am I?</t>
         </is>
       </c>
-      <c r="E411" t="inlineStr">
+      <c r="E411" s="31" t="inlineStr">
         <is>
           <t>A hard drive</t>
         </is>
       </c>
-      <c r="F411" t="inlineStr">
+      <c r="F411" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr">
+      <c r="G411" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H411" t="inlineStr">
+      <c r="H411" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="n">
+      <c r="A412" s="31" t="n">
         <v>411</v>
       </c>
-      <c r="B412" t="n">
+      <c r="B412" s="31" t="n">
         <v>59</v>
       </c>
-      <c r="C412" t="inlineStr">
+      <c r="C412" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr">
+      <c r="D412" s="31" t="inlineStr">
         <is>
           <t>A recipe of steps that a computer obeys, deciding what you see in a hundred small ways. What am I?</t>
         </is>
       </c>
-      <c r="E412" t="inlineStr">
+      <c r="E412" s="31" t="inlineStr">
         <is>
           <t>An algorithm</t>
         </is>
       </c>
-      <c r="F412" t="inlineStr">
+      <c r="F412" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr">
+      <c r="G412" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr">
+      <c r="H412" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="n">
+      <c r="A413" s="31" t="n">
         <v>412</v>
       </c>
-      <c r="B413" t="n">
+      <c r="B413" s="31" t="n">
         <v>59</v>
       </c>
-      <c r="C413" t="inlineStr">
+      <c r="C413" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr">
+      <c r="D413" s="31" t="inlineStr">
         <is>
           <t>Strap me to your face and the real world's gone; a make-believe place is suddenly on. What am I?</t>
         </is>
       </c>
-      <c r="E413" t="inlineStr">
+      <c r="E413" s="31" t="inlineStr">
         <is>
           <t>A VR headset</t>
         </is>
       </c>
-      <c r="F413" t="inlineStr">
+      <c r="F413" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr">
+      <c r="G413" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H413" t="inlineStr">
+      <c r="H413" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="n">
+      <c r="A414" s="31" t="n">
         <v>413</v>
       </c>
-      <c r="B414" t="n">
+      <c r="B414" s="31" t="n">
         <v>59</v>
       </c>
-      <c r="C414" t="inlineStr">
+      <c r="C414" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr">
+      <c r="D414" s="31" t="inlineStr">
         <is>
           <t>Layer by layer I build up a thing, from a digital plan to a physical ring. What am I?</t>
         </is>
       </c>
-      <c r="E414" t="inlineStr">
+      <c r="E414" s="31" t="inlineStr">
         <is>
           <t>A 3D printer</t>
         </is>
       </c>
-      <c r="F414" t="inlineStr">
+      <c r="F414" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G414" t="inlineStr">
+      <c r="G414" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H414" t="inlineStr">
+      <c r="H414" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="n">
+      <c r="A415" s="31" t="n">
         <v>414</v>
       </c>
-      <c r="B415" t="n">
+      <c r="B415" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="C415" t="inlineStr">
+      <c r="C415" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr">
+      <c r="D415" s="31" t="inlineStr">
         <is>
           <t>I sit in the corner with blinking green lights, sharing the internet through invisible flights. What am I?</t>
         </is>
       </c>
-      <c r="E415" t="inlineStr">
+      <c r="E415" s="31" t="inlineStr">
         <is>
           <t>A router</t>
         </is>
       </c>
-      <c r="F415" t="inlineStr">
+      <c r="F415" s="31" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="G415" t="inlineStr">
+      <c r="G415" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr">
+      <c r="H415" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="n">
+      <c r="A416" s="31" t="n">
         <v>415</v>
       </c>
-      <c r="B416" t="n">
+      <c r="B416" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="C416" t="inlineStr">
+      <c r="C416" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr">
+      <c r="D416" s="31" t="inlineStr">
         <is>
           <t>Up from the sub I poke through the sea, a tube with a mirror so the captain can see. What am I?</t>
         </is>
       </c>
-      <c r="E416" t="inlineStr">
+      <c r="E416" s="31" t="inlineStr">
         <is>
           <t>A periscope</t>
         </is>
       </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G416" t="inlineStr">
+      <c r="F416" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G416" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H416" t="inlineStr">
+      <c r="H416" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="n">
+      <c r="A417" s="31" t="n">
         <v>416</v>
       </c>
-      <c r="B417" t="n">
+      <c r="B417" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="C417" t="inlineStr">
+      <c r="C417" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr">
+      <c r="D417" s="31" t="inlineStr">
         <is>
           <t>My arms turn slow in the pushing breeze, grinding the grain or pumping with ease. What am I?</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr">
+      <c r="E417" s="31" t="inlineStr">
         <is>
           <t>A windmill</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G417" t="inlineStr">
+      <c r="F417" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G417" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H417" t="inlineStr">
+      <c r="H417" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="n">
+      <c r="A418" s="31" t="n">
         <v>417</v>
       </c>
-      <c r="B418" t="n">
+      <c r="B418" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="C418" t="inlineStr">
+      <c r="C418" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr">
+      <c r="D418" s="31" t="inlineStr">
         <is>
           <t>Stuffed with straw in a field I stand, frightening crows from the farmer's land. What am I?</t>
         </is>
       </c>
-      <c r="E418" t="inlineStr">
+      <c r="E418" s="31" t="inlineStr">
         <is>
           <t>A scarecrow</t>
         </is>
       </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G418" t="inlineStr">
+      <c r="F418" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G418" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H418" t="inlineStr">
+      <c r="H418" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="n">
+      <c r="A419" s="31" t="n">
         <v>418</v>
       </c>
-      <c r="B419" t="n">
+      <c r="B419" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="C419" t="inlineStr">
+      <c r="C419" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr">
+      <c r="D419" s="31" t="inlineStr">
         <is>
           <t>Bricks in a stack on the top of the house, I carry the smoke up and out, light as a mouse. What am I?</t>
         </is>
       </c>
-      <c r="E419" t="inlineStr">
+      <c r="E419" s="31" t="inlineStr">
         <is>
           <t>A chimney</t>
         </is>
       </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G419" t="inlineStr">
+      <c r="F419" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G419" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H419" t="inlineStr">
+      <c r="H419" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="n">
+      <c r="A420" s="31" t="n">
         <v>419</v>
       </c>
-      <c r="B420" t="n">
+      <c r="B420" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="C420" t="inlineStr">
+      <c r="C420" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr">
+      <c r="D420" s="31" t="inlineStr">
         <is>
           <t>Deep in the ground I hold the cool water; drop down a bucket, draw up what you sought here. What am I?</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr">
+      <c r="E420" s="31" t="inlineStr">
         <is>
           <t>A well</t>
         </is>
       </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G420" t="inlineStr">
+      <c r="F420" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G420" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H420" t="inlineStr">
+      <c r="H420" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="n">
+      <c r="A421" s="31" t="n">
         <v>420</v>
       </c>
-      <c r="B421" t="n">
+      <c r="B421" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="C421" t="inlineStr">
+      <c r="C421" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr">
+      <c r="D421" s="31" t="inlineStr">
         <is>
           <t>I throw up the water then catch it again, a dance in the square for the passing men. What am I?</t>
         </is>
       </c>
-      <c r="E421" t="inlineStr">
+      <c r="E421" s="31" t="inlineStr">
         <is>
           <t>A fountain</t>
         </is>
       </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G421" t="inlineStr">
+      <c r="F421" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G421" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H421" t="inlineStr">
+      <c r="H421" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="n">
+      <c r="A422" s="31" t="n">
         <v>421</v>
       </c>
-      <c r="B422" t="n">
+      <c r="B422" s="31" t="n">
         <v>61</v>
       </c>
-      <c r="C422" t="inlineStr">
+      <c r="C422" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr">
+      <c r="D422" s="31" t="inlineStr">
         <is>
           <t>I lift up my road to let the ships pass, then lower back down over moat or morass. What am I?</t>
         </is>
       </c>
-      <c r="E422" t="inlineStr">
+      <c r="E422" s="31" t="inlineStr">
         <is>
           <t>A drawbridge</t>
         </is>
       </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G422" t="inlineStr">
+      <c r="F422" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G422" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H422" t="inlineStr">
+      <c r="H422" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="n">
+      <c r="A423" s="31" t="n">
         <v>422</v>
       </c>
-      <c r="B423" t="n">
+      <c r="B423" s="31" t="n">
         <v>61</v>
       </c>
-      <c r="C423" t="inlineStr">
+      <c r="C423" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr">
+      <c r="D423" s="31" t="inlineStr">
         <is>
           <t>Round and round in a glass little cage, I let people in and out, all the rage. What am I?</t>
         </is>
       </c>
-      <c r="E423" t="inlineStr">
+      <c r="E423" s="31" t="inlineStr">
         <is>
           <t>A revolving door</t>
         </is>
       </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G423" t="inlineStr">
+      <c r="F423" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G423" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H423" t="inlineStr">
+      <c r="H423" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="n">
+      <c r="A424" s="31" t="n">
         <v>423</v>
       </c>
-      <c r="B424" t="n">
+      <c r="B424" s="31" t="n">
         <v>61</v>
       </c>
-      <c r="C424" t="inlineStr">
+      <c r="C424" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr">
+      <c r="D424" s="31" t="inlineStr">
         <is>
           <t>Feed me your coins and press a letter and number; a snack tumbles down from my well-lit chamber. What am I?</t>
         </is>
       </c>
-      <c r="E424" t="inlineStr">
+      <c r="E424" s="31" t="inlineStr">
         <is>
           <t>A vending machine</t>
         </is>
       </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G424" t="inlineStr">
+      <c r="F424" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G424" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H424" t="inlineStr">
+      <c r="H424" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="n">
+      <c r="A425" s="31" t="n">
         <v>424</v>
       </c>
-      <c r="B425" t="n">
+      <c r="B425" s="31" t="n">
         <v>61</v>
       </c>
-      <c r="C425" t="inlineStr">
+      <c r="C425" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr">
+      <c r="D425" s="31" t="inlineStr">
         <is>
           <t>Insert your card and punch in the code; I count out the cash that you're owed. What am I?</t>
         </is>
       </c>
-      <c r="E425" t="inlineStr">
+      <c r="E425" s="31" t="inlineStr">
         <is>
           <t>An ATM</t>
         </is>
       </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G425" t="inlineStr">
+      <c r="F425" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G425" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H425" t="inlineStr">
+      <c r="H425" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="n">
+      <c r="A426" s="31" t="n">
         <v>425</v>
       </c>
-      <c r="B426" t="n">
+      <c r="B426" s="31" t="n">
         <v>61</v>
       </c>
-      <c r="C426" t="inlineStr">
+      <c r="C426" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr">
+      <c r="D426" s="31" t="inlineStr">
         <is>
           <t>Orange and striped on the road I stand, warning the cars of the works at hand. What am I?</t>
         </is>
       </c>
-      <c r="E426" t="inlineStr">
+      <c r="E426" s="31" t="inlineStr">
         <is>
           <t>A traffic cone</t>
         </is>
       </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G426" t="inlineStr">
+      <c r="F426" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G426" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H426" t="inlineStr">
+      <c r="H426" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="n">
+      <c r="A427" s="31" t="n">
         <v>426</v>
       </c>
-      <c r="B427" t="n">
+      <c r="B427" s="31" t="n">
         <v>61</v>
       </c>
-      <c r="C427" t="inlineStr">
+      <c r="C427" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr">
+      <c r="D427" s="31" t="inlineStr">
         <is>
           <t>A ridge in the road to slow you down, I jolt the fast drivers all over town. What am I?</t>
         </is>
       </c>
-      <c r="E427" t="inlineStr">
+      <c r="E427" s="31" t="inlineStr">
         <is>
           <t>A speed bump</t>
         </is>
       </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G427" t="inlineStr">
+      <c r="F427" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G427" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H427" t="inlineStr">
+      <c r="H427" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="n">
+      <c r="A428" s="31" t="n">
         <v>427</v>
       </c>
-      <c r="B428" t="n">
+      <c r="B428" s="31" t="n">
         <v>61</v>
       </c>
-      <c r="C428" t="inlineStr">
+      <c r="C428" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr">
+      <c r="D428" s="31" t="inlineStr">
         <is>
           <t>A heavy round lid in the middle of the street, I hide the deep tunnels beneath your feet. What am I?</t>
         </is>
       </c>
-      <c r="E428" t="inlineStr">
+      <c r="E428" s="31" t="inlineStr">
         <is>
           <t>A manhole cover</t>
         </is>
       </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G428" t="inlineStr">
+      <c r="F428" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G428" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H428" t="inlineStr">
+      <c r="H428" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="n">
+      <c r="A429" s="31" t="n">
         <v>428</v>
       </c>
-      <c r="B429" t="n">
+      <c r="B429" s="31" t="n">
         <v>62</v>
       </c>
-      <c r="C429" t="inlineStr">
+      <c r="C429" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr">
+      <c r="D429" s="31" t="inlineStr">
         <is>
           <t>Red by the curb with a cap on each side, I give the firefighters water supplied. What am I?</t>
         </is>
       </c>
-      <c r="E429" t="inlineStr">
+      <c r="E429" s="31" t="inlineStr">
         <is>
           <t>A fire hydrant</t>
         </is>
       </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G429" t="inlineStr">
+      <c r="F429" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G429" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H429" t="inlineStr">
+      <c r="H429" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="n">
+      <c r="A430" s="31" t="n">
         <v>429</v>
       </c>
-      <c r="B430" t="n">
+      <c r="B430" s="31" t="n">
         <v>62</v>
       </c>
-      <c r="C430" t="inlineStr">
+      <c r="C430" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr">
+      <c r="D430" s="31" t="inlineStr">
         <is>
           <t>Flag up or down at the end of the drive, I hold your letters until they arrive. What am I?</t>
         </is>
       </c>
-      <c r="E430" t="inlineStr">
+      <c r="E430" s="31" t="inlineStr">
         <is>
           <t>A mailbox</t>
         </is>
       </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G430" t="inlineStr">
+      <c r="F430" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G430" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H430" t="inlineStr">
+      <c r="H430" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="n">
+      <c r="A431" s="31" t="n">
         <v>430</v>
       </c>
-      <c r="B431" t="n">
+      <c r="B431" s="31" t="n">
         <v>62</v>
       </c>
-      <c r="C431" t="inlineStr">
+      <c r="C431" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr">
+      <c r="D431" s="31" t="inlineStr">
         <is>
           <t>I spin on the lawn in the summer heat, throwing out water with a rhythmic beat. What am I?</t>
         </is>
       </c>
-      <c r="E431" t="inlineStr">
+      <c r="E431" s="31" t="inlineStr">
         <is>
           <t>A sprinkler</t>
         </is>
       </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G431" t="inlineStr">
+      <c r="F431" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G431" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H431" t="inlineStr">
+      <c r="H431" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="n">
+      <c r="A432" s="31" t="n">
         <v>431</v>
       </c>
-      <c r="B432" t="n">
+      <c r="B432" s="31" t="n">
         <v>62</v>
       </c>
-      <c r="C432" t="inlineStr">
+      <c r="C432" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr">
+      <c r="D432" s="31" t="inlineStr">
         <is>
           <t>I hum across the grass in rows, trimming it neat wherever it grows. What am I?</t>
         </is>
       </c>
-      <c r="E432" t="inlineStr">
+      <c r="E432" s="31" t="inlineStr">
         <is>
           <t>A lawnmower</t>
         </is>
       </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G432" t="inlineStr">
+      <c r="F432" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G432" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H432" t="inlineStr">
+      <c r="H432" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="n">
+      <c r="A433" s="31" t="n">
         <v>432</v>
       </c>
-      <c r="B433" t="n">
+      <c r="B433" s="31" t="n">
         <v>62</v>
       </c>
-      <c r="C433" t="inlineStr">
+      <c r="C433" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr">
+      <c r="D433" s="31" t="inlineStr">
         <is>
           <t>A wall made of leaves that the gardener clips, square and green at the garden's lips. What am I?</t>
         </is>
       </c>
-      <c r="E433" t="inlineStr">
+      <c r="E433" s="31" t="inlineStr">
         <is>
           <t>A hedge</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr">
+      <c r="F433" s="31" t="inlineStr">
         <is>
           <t>Nature</t>
         </is>
       </c>
-      <c r="G433" t="inlineStr">
+      <c r="G433" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H433" t="inlineStr">
+      <c r="H433" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="434">
-      <c r="A434" t="n">
+      <c r="A434" s="31" t="n">
         <v>433</v>
       </c>
-      <c r="B434" t="n">
+      <c r="B434" s="31" t="n">
         <v>62</v>
       </c>
-      <c r="C434" t="inlineStr">
+      <c r="C434" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr">
+      <c r="D434" s="31" t="inlineStr">
         <is>
           <t>Walls of glass where the plants stay warm, growing inside through the winter storm. What am I?</t>
         </is>
       </c>
-      <c r="E434" t="inlineStr">
+      <c r="E434" s="31" t="inlineStr">
         <is>
           <t>A greenhouse</t>
         </is>
       </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G434" t="inlineStr">
+      <c r="F434" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G434" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H434" t="inlineStr">
+      <c r="H434" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="435">
-      <c r="A435" t="n">
+      <c r="A435" s="31" t="n">
         <v>434</v>
       </c>
-      <c r="B435" t="n">
+      <c r="B435" s="31" t="n">
         <v>62</v>
       </c>
-      <c r="C435" t="inlineStr">
+      <c r="C435" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr">
+      <c r="D435" s="31" t="inlineStr">
         <is>
           <t>A little wooden box on a pole up high, a home with a hole where the sparrows fly. What am I?</t>
         </is>
       </c>
-      <c r="E435" t="inlineStr">
+      <c r="E435" s="31" t="inlineStr">
         <is>
           <t>A birdhouse</t>
         </is>
       </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G435" t="inlineStr">
+      <c r="F435" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G435" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H435" t="inlineStr">
+      <c r="H435" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="n">
+      <c r="A436" s="31" t="n">
         <v>435</v>
       </c>
-      <c r="B436" t="n">
+      <c r="B436" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="C436" t="inlineStr">
+      <c r="C436" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr">
+      <c r="D436" s="31" t="inlineStr">
         <is>
           <t>Drop in your coins through the slot on my back; I'm shaped like a pig and I keep the stack. What am I?</t>
         </is>
       </c>
-      <c r="E436" t="inlineStr">
+      <c r="E436" s="31" t="inlineStr">
         <is>
           <t>A piggy bank</t>
         </is>
       </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G436" t="inlineStr">
+      <c r="F436" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G436" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H436" t="inlineStr">
+      <c r="H436" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="n">
+      <c r="A437" s="31" t="n">
         <v>436</v>
       </c>
-      <c r="B437" t="n">
+      <c r="B437" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="C437" t="inlineStr">
+      <c r="C437" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr">
+      <c r="D437" s="31" t="inlineStr">
         <is>
           <t>Turn my crank and a tune starts to play, then I pop up to give you a fright and a sway. What am I?</t>
         </is>
       </c>
-      <c r="E437" t="inlineStr">
+      <c r="E437" s="31" t="inlineStr">
         <is>
           <t>A jack-in-the-box</t>
         </is>
       </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G437" t="inlineStr">
+      <c r="F437" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G437" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H437" t="inlineStr">
+      <c r="H437" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="n">
+      <c r="A438" s="31" t="n">
         <v>437</v>
       </c>
-      <c r="B438" t="n">
+      <c r="B438" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="C438" t="inlineStr">
+      <c r="C438" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr">
+      <c r="D438" s="31" t="inlineStr">
         <is>
           <t>Shake me up and a blizzard appears, over a tiny town, falling for years. What am I?</t>
         </is>
       </c>
-      <c r="E438" t="inlineStr">
+      <c r="E438" s="31" t="inlineStr">
         <is>
           <t>A snow globe</t>
         </is>
       </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G438" t="inlineStr">
+      <c r="F438" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G438" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr">
+      <c r="H438" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="n">
+      <c r="A439" s="31" t="n">
         <v>438</v>
       </c>
-      <c r="B439" t="n">
+      <c r="B439" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="C439" t="inlineStr">
+      <c r="C439" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr">
+      <c r="D439" s="31" t="inlineStr">
         <is>
           <t>Wind me up and a melody spins, a ballerina turns as the tune begins. What am I?</t>
         </is>
       </c>
-      <c r="E439" t="inlineStr">
+      <c r="E439" s="31" t="inlineStr">
         <is>
           <t>A music box</t>
         </is>
       </c>
-      <c r="F439" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G439" t="inlineStr">
+      <c r="F439" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G439" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H439" t="inlineStr">
+      <c r="H439" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="440">
-      <c r="A440" t="n">
+      <c r="A440" s="31" t="n">
         <v>439</v>
       </c>
-      <c r="B440" t="n">
+      <c r="B440" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="C440" t="inlineStr">
+      <c r="C440" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr">
+      <c r="D440" s="31" t="inlineStr">
         <is>
           <t>I swing on a handle with a flame held within, lighting the path through the dark and the din. What am I?</t>
         </is>
       </c>
-      <c r="E440" t="inlineStr">
+      <c r="E440" s="31" t="inlineStr">
         <is>
           <t>A lantern</t>
         </is>
       </c>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G440" t="inlineStr">
+      <c r="F440" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G440" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H440" t="inlineStr">
+      <c r="H440" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="n">
+      <c r="A441" s="31" t="n">
         <v>440</v>
       </c>
-      <c r="B441" t="n">
+      <c r="B441" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="C441" t="inlineStr">
+      <c r="C441" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr">
+      <c r="D441" s="31" t="inlineStr">
         <is>
           <t>A beam from my end when I'm clicked on at night, I fit in your hand and I throw out the light. What am I?</t>
         </is>
       </c>
-      <c r="E441" t="inlineStr">
+      <c r="E441" s="31" t="inlineStr">
         <is>
           <t>A flashlight</t>
         </is>
       </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G441" t="inlineStr">
+      <c r="F441" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G441" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H441" t="inlineStr">
+      <c r="H441" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="442">
-      <c r="A442" t="n">
+      <c r="A442" s="31" t="n">
         <v>441</v>
       </c>
-      <c r="B442" t="n">
+      <c r="B442" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="C442" t="inlineStr">
+      <c r="C442" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr">
+      <c r="D442" s="31" t="inlineStr">
         <is>
           <t>The whole world spun on a tilted stand, I show every ocean and every land. What am I?</t>
         </is>
       </c>
-      <c r="E442" t="inlineStr">
+      <c r="E442" s="31" t="inlineStr">
         <is>
           <t>A globe</t>
         </is>
       </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G442" t="inlineStr">
+      <c r="F442" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G442" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H442" t="inlineStr">
+      <c r="H442" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="n">
+      <c r="A443" s="31" t="n">
         <v>442</v>
       </c>
-      <c r="B443" t="n">
+      <c r="B443" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="C443" t="inlineStr">
+      <c r="C443" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr">
+      <c r="D443" s="31" t="inlineStr">
         <is>
           <t>Beads on wires that slide to and fro, I count up the sums in an ancient row. What am I?</t>
         </is>
       </c>
-      <c r="E443" t="inlineStr">
+      <c r="E443" s="31" t="inlineStr">
         <is>
           <t>An abacus</t>
         </is>
       </c>
-      <c r="F443" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G443" t="inlineStr">
+      <c r="F443" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G443" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H443" t="inlineStr">
+      <c r="H443" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="n">
+      <c r="A444" s="31" t="n">
         <v>443</v>
       </c>
-      <c r="B444" t="n">
+      <c r="B444" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="C444" t="inlineStr">
+      <c r="C444" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr">
+      <c r="D444" s="31" t="inlineStr">
         <is>
           <t>A half-moon of plastic with numbers in a bow, I measure the angles so the students know. What am I?</t>
         </is>
       </c>
-      <c r="E444" t="inlineStr">
+      <c r="E444" s="31" t="inlineStr">
         <is>
           <t>A protractor</t>
         </is>
       </c>
-      <c r="F444" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G444" t="inlineStr">
+      <c r="F444" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G444" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H444" t="inlineStr">
+      <c r="H444" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="445">
-      <c r="A445" t="n">
+      <c r="A445" s="31" t="n">
         <v>444</v>
       </c>
-      <c r="B445" t="n">
+      <c r="B445" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="C445" t="inlineStr">
+      <c r="C445" s="31" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr">
+      <c r="D445" s="31" t="inlineStr">
         <is>
           <t>Twist the pencil in my little hole and out come the shavings as I take my toll. What am I?</t>
         </is>
       </c>
-      <c r="E445" t="inlineStr">
+      <c r="E445" s="31" t="inlineStr">
         <is>
           <t>A pencil sharpener</t>
         </is>
       </c>
-      <c r="F445" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G445" t="inlineStr">
+      <c r="F445" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G445" s="31" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="H445" t="inlineStr">
+      <c r="H445" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="n">
+      <c r="A446" s="31" t="n">
         <v>445</v>
       </c>
-      <c r="B446" t="n">
+      <c r="B446" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="C446" t="inlineStr">
+      <c r="C446" s="31" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr">
+      <c r="D446" s="31" t="inlineStr">
         <is>
           <t>I bite two round holes in the edge of the sheet so it fits in the binder, tidy and neat. What am I?</t>
         </is>
       </c>
-      <c r="E446" t="inlineStr">
+      <c r="E446" s="31" t="inlineStr">
         <is>
           <t>A hole punch</t>
         </is>
       </c>
-      <c r="F446" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G446" t="inlineStr">
+      <c r="F446" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G446" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H446" t="inlineStr">
+      <c r="H446" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="n">
+      <c r="A447" s="31" t="n">
         <v>446</v>
       </c>
-      <c r="B447" t="n">
+      <c r="B447" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="C447" t="inlineStr">
+      <c r="C447" s="31" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr">
+      <c r="D447" s="31" t="inlineStr">
         <is>
           <t>I sit on your desk doing nothing but weigh, keeping the papers from blowing away. What am I?</t>
         </is>
       </c>
-      <c r="E447" t="inlineStr">
+      <c r="E447" s="31" t="inlineStr">
         <is>
           <t>A paperweight</t>
         </is>
       </c>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G447" t="inlineStr">
+      <c r="F447" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G447" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H447" t="inlineStr">
+      <c r="H447" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="n">
+      <c r="A448" s="31" t="n">
         <v>447</v>
       </c>
-      <c r="B448" t="n">
+      <c r="B448" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="C448" t="inlineStr">
+      <c r="C448" s="31" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr">
+      <c r="D448" s="31" t="inlineStr">
         <is>
           <t>A little metal cap for the fingertip, I guard against the needle's prick and slip. What am I?</t>
         </is>
       </c>
-      <c r="E448" t="inlineStr">
+      <c r="E448" s="31" t="inlineStr">
         <is>
           <t>A thimble</t>
         </is>
       </c>
-      <c r="F448" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G448" t="inlineStr">
+      <c r="F448" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G448" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H448" t="inlineStr">
+      <c r="H448" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="n">
+      <c r="A449" s="31" t="n">
         <v>448</v>
       </c>
-      <c r="B449" t="n">
+      <c r="B449" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="C449" t="inlineStr">
+      <c r="C449" s="31" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr">
+      <c r="D449" s="31" t="inlineStr">
         <is>
           <t>Thread wound around me in a tidy reel, I feed the machine that sews the seam real. What am I?</t>
         </is>
       </c>
-      <c r="E449" t="inlineStr">
+      <c r="E449" s="31" t="inlineStr">
         <is>
           <t>A spool</t>
         </is>
       </c>
-      <c r="F449" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G449" t="inlineStr">
+      <c r="F449" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G449" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H449" t="inlineStr">
+      <c r="H449" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="n">
+      <c r="A450" s="31" t="n">
         <v>449</v>
       </c>
-      <c r="B450" t="n">
+      <c r="B450" s="31" t="n">
         <v>65</v>
       </c>
-      <c r="C450" t="inlineStr">
+      <c r="C450" s="31" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr">
+      <c r="D450" s="31" t="inlineStr">
         <is>
           <t>Threads stretched tight in a crossing dance, I weave the cloth thread by thread, not by chance. What am I?</t>
         </is>
       </c>
-      <c r="E450" t="inlineStr">
+      <c r="E450" s="31" t="inlineStr">
         <is>
           <t>A loom</t>
         </is>
       </c>
-      <c r="F450" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G450" t="inlineStr">
+      <c r="F450" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G450" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H450" t="inlineStr">
+      <c r="H450" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="n">
+      <c r="A451" s="31" t="n">
         <v>450</v>
       </c>
-      <c r="B451" t="n">
+      <c r="B451" s="31" t="n">
         <v>65</v>
       </c>
-      <c r="C451" t="inlineStr">
+      <c r="C451" s="31" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr">
+      <c r="D451" s="31" t="inlineStr">
         <is>
           <t>A furnace of fire where the clay is baked, hardening the pots that the potter made. What am I?</t>
         </is>
       </c>
-      <c r="E451" t="inlineStr">
+      <c r="E451" s="31" t="inlineStr">
         <is>
           <t>A kiln</t>
         </is>
       </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="G451" t="inlineStr">
+      <c r="F451" s="31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="G451" s="31" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="H451" t="inlineStr">
+      <c r="H451" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
